--- a/epsilon-phi-core/src/Scripts/Case Studies/1. Portfolio Analysis/Simple Portfolio Report_new_pe.xlsx
+++ b/epsilon-phi-core/src/Scripts/Case Studies/1. Portfolio Analysis/Simple Portfolio Report_new_pe.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/francisbarker/Repositories/Python/epsilon-phi/epsilon-phi-core/src/Scripts/Case Studies/1. Portfolio Analysis/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/francisbarker/repo/epsilon-psi/epsilon-phi-core/src/Scripts/Case Studies/1. Portfolio Analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DE9C429-B145-EF48-BA96-9EB80FE03BBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F469C6C1-D1F0-284B-8ECD-3F07464E8F37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2200" yWindow="1240" windowWidth="49600" windowHeight="24840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="19040" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="portfolios" sheetId="1" r:id="rId1"/>
@@ -875,13 +875,10 @@
     <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="10" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="10" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -889,18 +886,21 @@
     <xf numFmtId="2" fontId="10" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -7838,7 +7838,7 @@
                   <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="en-US"/>
+              <a:endParaRPr lang="en-GB"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -22377,24 +22377,24 @@
   <sheetData>
     <row r="1" spans="1:5" ht="41" customHeight="1">
       <c r="A1" s="42"/>
-      <c r="B1" s="62" t="s">
+      <c r="B1" s="67" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="63"/>
-      <c r="D1" s="71" t="s">
+      <c r="D1" s="68" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="72"/>
+      <c r="E1" s="69"/>
     </row>
     <row r="2" spans="1:5" ht="16" customHeight="1">
       <c r="A2" s="44" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="64">
+      <c r="B2" s="62">
         <v>0.5</v>
       </c>
       <c r="C2" s="63"/>
-      <c r="D2" s="64">
+      <c r="D2" s="62">
         <v>0.36</v>
       </c>
       <c r="E2" s="63"/>
@@ -22403,11 +22403,11 @@
       <c r="A3" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="64" t="s">
+      <c r="B3" s="62" t="s">
         <v>150</v>
       </c>
       <c r="C3" s="63"/>
-      <c r="D3" s="64">
+      <c r="D3" s="62">
         <v>4.4999999999999998E-2</v>
       </c>
       <c r="E3" s="63"/>
@@ -22416,11 +22416,11 @@
       <c r="A4" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="64">
+      <c r="B4" s="62">
         <v>0.5</v>
       </c>
       <c r="C4" s="63"/>
-      <c r="D4" s="64">
+      <c r="D4" s="62">
         <v>0.35499999999999998</v>
       </c>
       <c r="E4" s="63"/>
@@ -22429,11 +22429,11 @@
       <c r="A5" s="44" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="64" t="s">
+      <c r="B5" s="62" t="s">
         <v>150</v>
       </c>
       <c r="C5" s="63"/>
-      <c r="D5" s="64">
+      <c r="D5" s="62">
         <v>4.5000000000000012E-2</v>
       </c>
       <c r="E5" s="63"/>
@@ -22442,11 +22442,11 @@
       <c r="A6" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="64" t="s">
+      <c r="B6" s="62" t="s">
         <v>150</v>
       </c>
       <c r="C6" s="63"/>
-      <c r="D6" s="64">
+      <c r="D6" s="62">
         <v>0.12</v>
       </c>
       <c r="E6" s="63"/>
@@ -22455,11 +22455,11 @@
       <c r="A7" s="44" t="s">
         <v>26</v>
       </c>
-      <c r="B7" s="64" t="s">
+      <c r="B7" s="62" t="s">
         <v>150</v>
       </c>
       <c r="C7" s="63"/>
-      <c r="D7" s="64">
+      <c r="D7" s="62">
         <v>7.5000000000000011E-2</v>
       </c>
       <c r="E7" s="63"/>
@@ -22468,24 +22468,24 @@
       <c r="A8" s="46" t="s">
         <v>31</v>
       </c>
-      <c r="B8" s="65">
+      <c r="B8" s="64">
         <v>5.3832602562404443E-2</v>
       </c>
-      <c r="C8" s="66"/>
-      <c r="D8" s="65">
+      <c r="C8" s="65"/>
+      <c r="D8" s="64">
         <v>6.4431104932666197E-2</v>
       </c>
-      <c r="E8" s="66"/>
+      <c r="E8" s="65"/>
     </row>
     <row r="9" spans="1:5" ht="16" customHeight="1">
       <c r="A9" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="B9" s="67">
+      <c r="B9" s="66">
         <v>0.39013325979698232</v>
       </c>
       <c r="C9" s="63"/>
-      <c r="D9" s="67">
+      <c r="D9" s="66">
         <v>0.52364381017028427</v>
       </c>
       <c r="E9" s="63"/>
@@ -22494,11 +22494,11 @@
       <c r="A10" s="44" t="s">
         <v>33</v>
       </c>
-      <c r="B10" s="64">
+      <c r="B10" s="62">
         <v>7.3904497600149111E-2</v>
       </c>
       <c r="C10" s="63"/>
-      <c r="D10" s="64">
+      <c r="D10" s="62">
         <v>7.5095139422881152E-2</v>
       </c>
       <c r="E10" s="63"/>
@@ -22936,6 +22936,18 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="D6:E6"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="D10:E10"/>
     <mergeCell ref="B7:C7"/>
@@ -22944,18 +22956,6 @@
     <mergeCell ref="D8:E8"/>
     <mergeCell ref="B9:C9"/>
     <mergeCell ref="D9:E9"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="D3:E3"/>
   </mergeCells>
   <conditionalFormatting sqref="B13:E21">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
@@ -22985,27 +22985,27 @@
   <sheetData>
     <row r="1" spans="1:10" ht="24" customHeight="1">
       <c r="A1" s="1"/>
-      <c r="B1" s="68" t="s">
+      <c r="B1" s="70" t="s">
         <v>53</v>
       </c>
-      <c r="C1" s="69"/>
-      <c r="D1" s="69"/>
-      <c r="E1" s="69"/>
-      <c r="F1" s="69"/>
-      <c r="G1" s="69"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="71"/>
+      <c r="F1" s="71"/>
+      <c r="G1" s="71"/>
       <c r="H1" s="3"/>
-      <c r="I1" s="68" t="s">
+      <c r="I1" s="70" t="s">
         <v>54</v>
       </c>
-      <c r="J1" s="69"/>
+      <c r="J1" s="71"/>
     </row>
     <row r="2" spans="1:10" ht="49" customHeight="1">
       <c r="A2" s="4"/>
-      <c r="B2" s="70" t="s">
+      <c r="B2" s="72" t="s">
         <v>55</v>
       </c>
-      <c r="C2" s="69"/>
-      <c r="D2" s="69"/>
+      <c r="C2" s="71"/>
+      <c r="D2" s="71"/>
       <c r="E2" s="2" t="s">
         <v>33</v>
       </c>

--- a/epsilon-phi-core/src/Scripts/Case Studies/1. Portfolio Analysis/Simple Portfolio Report_new_pe.xlsx
+++ b/epsilon-phi-core/src/Scripts/Case Studies/1. Portfolio Analysis/Simple Portfolio Report_new_pe.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/francisbarker/Repositories/Python/epsilon-phi/epsilon-phi-core/src/Scripts/Case Studies/1. Portfolio Analysis/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/francisbarker/repo/epsilon-psi/epsilon-phi-core/src/Scripts/Case Studies/1. Portfolio Analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C4E3263-4785-1E45-89E9-A229CD964E3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CB2D1C3-6880-DC48-8FC8-04065BF04204}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3080" yWindow="2300" windowWidth="33600" windowHeight="19040" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="19040" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="portfolios" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="157">
   <si>
     <t>Reference</t>
   </si>
@@ -504,6 +504,21 @@
   <si>
     <t>Estimated Mean Return (with 2.5% Risk Free Rate)</t>
   </si>
+  <si>
+    <t>Other</t>
+  </si>
+  <si>
+    <t>AUD</t>
+  </si>
+  <si>
+    <t>CNY</t>
+  </si>
+  <si>
+    <t>TWD</t>
+  </si>
+  <si>
+    <t>INR</t>
+  </si>
 </sst>
 </file>
 
@@ -944,7 +959,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="102">
+  <cellXfs count="104">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1054,7 +1069,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="7" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1076,20 +1090,6 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="2" fontId="10" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1139,24 +1139,8 @@
     <xf numFmtId="0" fontId="9" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1207,6 +1191,41 @@
     <xf numFmtId="0" fontId="9" fillId="6" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
+    <xf numFmtId="2" fontId="10" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1215,17 +1234,17 @@
   <dxfs count="3">
     <dxf>
       <font>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF006100"/>
       </font>
     </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
       </font>
     </dxf>
   </dxfs>
@@ -8375,9 +8394,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'Risk Decomposition'!$A$41:$A$45</c:f>
+              <c:f>'Risk Decomposition'!$A$41:$A$46</c:f>
               <c:strCache>
-                <c:ptCount val="5"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>EUR</c:v>
                 </c:pt>
@@ -8388,20 +8407,23 @@
                   <c:v>JPY</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>Asia-Pacific Equity</c:v>
+                  <c:v>AUD</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>EM</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Other</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Risk Decomposition'!$B$41:$B$45</c:f>
+              <c:f>'Risk Decomposition'!$B$41:$B$46</c:f>
               <c:numCache>
                 <c:formatCode>0.0%</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>1.9086594707416901E-2</c:v>
                 </c:pt>
@@ -8412,10 +8434,13 @@
                   <c:v>3.5395217114644602E-3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>8.3038021272114002E-3</c:v>
+                  <c:v>5.0000000000000001E-3</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>5.8650377463103599E-3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3.3038021272114027E-3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8445,19 +8470,34 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
         <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
+        <c:majorTickMark val="cross"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:noFill/>
           <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
+              <a:schemeClr val="dk1">
+                <a:shade val="95000"/>
+                <a:satMod val="105000"/>
               </a:schemeClr>
             </a:solidFill>
+            <a:prstDash val="solid"/>
             <a:round/>
           </a:ln>
           <a:effectLst/>
@@ -8474,7 +8514,7 @@
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
+                <a:latin typeface="Aptos" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
                 <a:ea typeface="+mn-ea"/>
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
@@ -8496,28 +8536,20 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
         <c:numFmt formatCode="0.0%" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:noFill/>
-          <a:ln>
-            <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="dk1">
+                <a:shade val="95000"/>
+                <a:satMod val="105000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
           </a:ln>
           <a:effectLst/>
         </c:spPr>
@@ -8533,7 +8565,7 @@
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
+                <a:latin typeface="Aptos" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
                 <a:ea typeface="+mn-ea"/>
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
@@ -8565,16 +8597,9 @@
     <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
+    <a:noFill/>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
+      <a:noFill/>
       <a:round/>
     </a:ln>
     <a:effectLst/>
@@ -8584,7 +8609,9 @@
     <a:lstStyle/>
     <a:p>
       <a:pPr>
-        <a:defRPr/>
+        <a:defRPr b="0" i="0">
+          <a:latin typeface="Aptos" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+        </a:defRPr>
       </a:pPr>
       <a:endParaRPr lang="en-US"/>
     </a:p>
@@ -8656,7 +8683,7 @@
                   <c:v>JPY</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>Asia-Pacific Equity</c:v>
+                  <c:v>AUD</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>EM</c:v>
@@ -8680,7 +8707,7 @@
                   <c:v>3.5395217114644602E-3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>8.3038021272114002E-3</c:v>
+                  <c:v>5.0000000000000001E-3</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>5.8650377463103599E-3</c:v>
@@ -17039,16 +17066,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>471714</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>179614</xdr:rowOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>807357</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>52614</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>90714</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>65314</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>426357</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>128814</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -17875,433 +17902,433 @@
     </row>
     <row r="2" spans="1:5" ht="43" customHeight="1">
       <c r="A2" s="40"/>
-      <c r="B2" s="56"/>
-      <c r="C2" s="57" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="58" t="s">
+      <c r="B2" s="49"/>
+      <c r="C2" s="50" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="51" t="s">
         <v>1</v>
       </c>
       <c r="E2" s="40"/>
     </row>
     <row r="3" spans="1:5" ht="17" customHeight="1">
       <c r="A3" s="40"/>
-      <c r="B3" s="59" t="s">
+      <c r="B3" s="52" t="s">
         <v>2</v>
       </c>
       <c r="C3" s="30">
         <v>0.5</v>
       </c>
-      <c r="D3" s="60">
+      <c r="D3" s="53">
         <v>0.36</v>
       </c>
       <c r="E3" s="40"/>
     </row>
     <row r="4" spans="1:5" ht="17" customHeight="1">
       <c r="A4" s="40"/>
-      <c r="B4" s="61" t="s">
+      <c r="B4" s="54" t="s">
         <v>3</v>
       </c>
       <c r="C4" s="31">
         <v>50</v>
       </c>
-      <c r="D4" s="62">
+      <c r="D4" s="55">
         <v>36</v>
       </c>
       <c r="E4" s="40"/>
     </row>
     <row r="5" spans="1:5" ht="17" customHeight="1">
       <c r="A5" s="40"/>
-      <c r="B5" s="59" t="s">
+      <c r="B5" s="52" t="s">
         <v>4</v>
       </c>
       <c r="C5" s="30"/>
-      <c r="D5" s="60">
+      <c r="D5" s="53">
         <v>4.4999999999999998E-2</v>
       </c>
       <c r="E5" s="40"/>
     </row>
     <row r="6" spans="1:5" ht="17" customHeight="1">
       <c r="A6" s="40"/>
-      <c r="B6" s="61" t="s">
+      <c r="B6" s="54" t="s">
         <v>5</v>
       </c>
       <c r="C6" s="31">
         <v>0</v>
       </c>
-      <c r="D6" s="62">
+      <c r="D6" s="55">
         <v>4.5</v>
       </c>
       <c r="E6" s="40"/>
     </row>
     <row r="7" spans="1:5" ht="17" customHeight="1">
       <c r="A7" s="40"/>
-      <c r="B7" s="59" t="s">
+      <c r="B7" s="52" t="s">
         <v>6</v>
       </c>
       <c r="C7" s="30">
         <v>0.5</v>
       </c>
-      <c r="D7" s="60">
+      <c r="D7" s="53">
         <v>0.35499999999999998</v>
       </c>
       <c r="E7" s="40"/>
     </row>
     <row r="8" spans="1:5" ht="17" customHeight="1">
       <c r="A8" s="40"/>
-      <c r="B8" s="61" t="s">
+      <c r="B8" s="54" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="31">
         <v>50</v>
       </c>
-      <c r="D8" s="62">
+      <c r="D8" s="55">
         <v>0</v>
       </c>
       <c r="E8" s="40"/>
     </row>
     <row r="9" spans="1:5" ht="17" customHeight="1">
       <c r="A9" s="40"/>
-      <c r="B9" s="61" t="s">
+      <c r="B9" s="54" t="s">
         <v>8</v>
       </c>
       <c r="C9" s="31">
         <v>0</v>
       </c>
-      <c r="D9" s="62">
+      <c r="D9" s="55">
         <v>10</v>
       </c>
       <c r="E9" s="40"/>
     </row>
     <row r="10" spans="1:5" ht="17" customHeight="1">
       <c r="A10" s="40"/>
-      <c r="B10" s="61" t="s">
+      <c r="B10" s="54" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="31">
         <v>0</v>
       </c>
-      <c r="D10" s="62">
+      <c r="D10" s="55">
         <v>11.2</v>
       </c>
       <c r="E10" s="40"/>
     </row>
     <row r="11" spans="1:5" ht="17" customHeight="1">
       <c r="A11" s="40"/>
-      <c r="B11" s="61" t="s">
+      <c r="B11" s="54" t="s">
         <v>10</v>
       </c>
       <c r="C11" s="31">
         <v>0</v>
       </c>
-      <c r="D11" s="62">
+      <c r="D11" s="55">
         <v>3.5</v>
       </c>
       <c r="E11" s="40"/>
     </row>
     <row r="12" spans="1:5" ht="17" customHeight="1">
       <c r="A12" s="40"/>
-      <c r="B12" s="61" t="s">
+      <c r="B12" s="54" t="s">
         <v>11</v>
       </c>
       <c r="C12" s="31">
         <v>0</v>
       </c>
-      <c r="D12" s="62">
+      <c r="D12" s="55">
         <v>4</v>
       </c>
       <c r="E12" s="40"/>
     </row>
     <row r="13" spans="1:5" ht="17" customHeight="1">
       <c r="A13" s="40"/>
-      <c r="B13" s="61" t="s">
+      <c r="B13" s="54" t="s">
         <v>12</v>
       </c>
       <c r="C13" s="31">
         <v>0</v>
       </c>
-      <c r="D13" s="62">
+      <c r="D13" s="55">
         <v>1.2</v>
       </c>
       <c r="E13" s="40"/>
     </row>
     <row r="14" spans="1:5" ht="17" customHeight="1">
       <c r="A14" s="40"/>
-      <c r="B14" s="61" t="s">
+      <c r="B14" s="54" t="s">
         <v>13</v>
       </c>
       <c r="C14" s="31">
         <v>0</v>
       </c>
-      <c r="D14" s="62">
+      <c r="D14" s="55">
         <v>1.8</v>
       </c>
       <c r="E14" s="40"/>
     </row>
     <row r="15" spans="1:5" ht="17" customHeight="1">
       <c r="A15" s="40"/>
-      <c r="B15" s="61" t="s">
+      <c r="B15" s="54" t="s">
         <v>14</v>
       </c>
       <c r="C15" s="31">
         <v>0</v>
       </c>
-      <c r="D15" s="62">
+      <c r="D15" s="55">
         <v>0.90000000000000013</v>
       </c>
       <c r="E15" s="40"/>
     </row>
     <row r="16" spans="1:5" ht="17" customHeight="1">
       <c r="A16" s="40"/>
-      <c r="B16" s="61" t="s">
+      <c r="B16" s="54" t="s">
         <v>15</v>
       </c>
       <c r="C16" s="31">
         <v>0</v>
       </c>
-      <c r="D16" s="62">
+      <c r="D16" s="55">
         <v>0.90000000000000013</v>
       </c>
       <c r="E16" s="40"/>
     </row>
     <row r="17" spans="1:5" ht="17" customHeight="1">
       <c r="A17" s="40"/>
-      <c r="B17" s="61" t="s">
+      <c r="B17" s="54" t="s">
         <v>16</v>
       </c>
       <c r="C17" s="31">
         <v>0</v>
       </c>
-      <c r="D17" s="62">
+      <c r="D17" s="55">
         <v>1</v>
       </c>
       <c r="E17" s="40"/>
     </row>
     <row r="18" spans="1:5" ht="17" customHeight="1">
       <c r="A18" s="40"/>
-      <c r="B18" s="61" t="s">
+      <c r="B18" s="54" t="s">
         <v>17</v>
       </c>
       <c r="C18" s="31">
         <v>0</v>
       </c>
-      <c r="D18" s="62">
+      <c r="D18" s="55">
         <v>1</v>
       </c>
       <c r="E18" s="40"/>
     </row>
     <row r="19" spans="1:5" ht="17" customHeight="1">
       <c r="A19" s="40"/>
-      <c r="B19" s="59" t="s">
+      <c r="B19" s="52" t="s">
         <v>18</v>
       </c>
       <c r="C19" s="30"/>
-      <c r="D19" s="60">
+      <c r="D19" s="53">
         <v>4.5000000000000012E-2</v>
       </c>
       <c r="E19" s="40"/>
     </row>
     <row r="20" spans="1:5" ht="17" customHeight="1">
       <c r="A20" s="40"/>
-      <c r="B20" s="61" t="s">
+      <c r="B20" s="54" t="s">
         <v>19</v>
       </c>
       <c r="C20" s="31">
         <v>0</v>
       </c>
-      <c r="D20" s="62">
+      <c r="D20" s="55">
         <v>0.90000000000000013</v>
       </c>
       <c r="E20" s="40"/>
     </row>
     <row r="21" spans="1:5" ht="17" customHeight="1">
       <c r="A21" s="40"/>
-      <c r="B21" s="61" t="s">
+      <c r="B21" s="54" t="s">
         <v>20</v>
       </c>
       <c r="C21" s="31">
         <v>0</v>
       </c>
-      <c r="D21" s="62">
+      <c r="D21" s="55">
         <v>1.8</v>
       </c>
       <c r="E21" s="40"/>
     </row>
     <row r="22" spans="1:5" ht="17" customHeight="1">
       <c r="A22" s="40"/>
-      <c r="B22" s="61" t="s">
+      <c r="B22" s="54" t="s">
         <v>21</v>
       </c>
       <c r="C22" s="31">
         <v>0</v>
       </c>
-      <c r="D22" s="62">
+      <c r="D22" s="55">
         <v>1.8</v>
       </c>
       <c r="E22" s="40"/>
     </row>
     <row r="23" spans="1:5" ht="17" customHeight="1">
       <c r="A23" s="40"/>
-      <c r="B23" s="59" t="s">
+      <c r="B23" s="52" t="s">
         <v>22</v>
       </c>
       <c r="C23" s="30"/>
-      <c r="D23" s="60">
+      <c r="D23" s="53">
         <v>0.12</v>
       </c>
       <c r="E23" s="40"/>
     </row>
     <row r="24" spans="1:5" ht="17" customHeight="1">
       <c r="A24" s="40"/>
-      <c r="B24" s="61" t="s">
+      <c r="B24" s="54" t="s">
         <v>23</v>
       </c>
       <c r="C24" s="31">
         <v>0</v>
       </c>
-      <c r="D24" s="62">
+      <c r="D24" s="55">
         <v>8.4</v>
       </c>
       <c r="E24" s="40"/>
     </row>
     <row r="25" spans="1:5" ht="17" customHeight="1">
       <c r="A25" s="40"/>
-      <c r="B25" s="61" t="s">
+      <c r="B25" s="54" t="s">
         <v>24</v>
       </c>
       <c r="C25" s="31">
         <v>0</v>
       </c>
-      <c r="D25" s="62">
+      <c r="D25" s="55">
         <v>2.8</v>
       </c>
       <c r="E25" s="40"/>
     </row>
     <row r="26" spans="1:5" ht="17" customHeight="1">
       <c r="A26" s="40"/>
-      <c r="B26" s="61" t="s">
+      <c r="B26" s="54" t="s">
         <v>25</v>
       </c>
       <c r="C26" s="31">
         <v>0</v>
       </c>
-      <c r="D26" s="62">
+      <c r="D26" s="55">
         <v>0.8</v>
       </c>
       <c r="E26" s="40"/>
     </row>
     <row r="27" spans="1:5" ht="17" customHeight="1">
       <c r="A27" s="40"/>
-      <c r="B27" s="59" t="s">
+      <c r="B27" s="52" t="s">
         <v>26</v>
       </c>
       <c r="C27" s="30"/>
-      <c r="D27" s="60">
+      <c r="D27" s="53">
         <v>7.5000000000000011E-2</v>
       </c>
       <c r="E27" s="40"/>
     </row>
     <row r="28" spans="1:5" ht="17" customHeight="1">
       <c r="A28" s="40"/>
-      <c r="B28" s="61" t="s">
+      <c r="B28" s="54" t="s">
         <v>27</v>
       </c>
       <c r="C28" s="31">
         <v>0</v>
       </c>
-      <c r="D28" s="62">
+      <c r="D28" s="55">
         <v>3.5</v>
       </c>
       <c r="E28" s="40"/>
     </row>
     <row r="29" spans="1:5" ht="17" customHeight="1">
       <c r="A29" s="40"/>
-      <c r="B29" s="61" t="s">
+      <c r="B29" s="54" t="s">
         <v>28</v>
       </c>
       <c r="C29" s="31">
         <v>0</v>
       </c>
-      <c r="D29" s="62">
+      <c r="D29" s="55">
         <v>2</v>
       </c>
       <c r="E29" s="40"/>
     </row>
     <row r="30" spans="1:5" ht="17" customHeight="1">
       <c r="A30" s="40"/>
-      <c r="B30" s="61" t="s">
+      <c r="B30" s="54" t="s">
         <v>29</v>
       </c>
       <c r="C30" s="31">
         <v>0</v>
       </c>
-      <c r="D30" s="62">
+      <c r="D30" s="55">
         <v>2</v>
       </c>
       <c r="E30" s="40"/>
     </row>
     <row r="31" spans="1:5" ht="23" customHeight="1">
       <c r="A31" s="40"/>
-      <c r="B31" s="63" t="s">
+      <c r="B31" s="56" t="s">
         <v>30</v>
       </c>
       <c r="C31" s="32">
         <v>1</v>
       </c>
-      <c r="D31" s="64">
+      <c r="D31" s="57">
         <v>1</v>
       </c>
       <c r="E31" s="40"/>
     </row>
     <row r="32" spans="1:5" ht="3" customHeight="1">
       <c r="A32" s="40"/>
-      <c r="B32" s="65"/>
+      <c r="B32" s="58"/>
       <c r="C32" s="33"/>
-      <c r="D32" s="66"/>
+      <c r="D32" s="59"/>
       <c r="E32" s="40"/>
     </row>
     <row r="33" spans="1:5" ht="23" customHeight="1">
       <c r="A33" s="40"/>
-      <c r="B33" s="67" t="s">
+      <c r="B33" s="60" t="s">
         <v>141</v>
       </c>
       <c r="C33" s="34">
         <v>5.3832602562404443E-2</v>
       </c>
-      <c r="D33" s="68">
+      <c r="D33" s="61">
         <v>6.4431104932666197E-2</v>
       </c>
       <c r="E33" s="40"/>
     </row>
     <row r="34" spans="1:5" ht="23" customHeight="1">
       <c r="A34" s="40"/>
-      <c r="B34" s="67" t="s">
+      <c r="B34" s="60" t="s">
         <v>31</v>
       </c>
       <c r="C34" s="35">
         <v>0.39013325979698232</v>
       </c>
-      <c r="D34" s="69">
+      <c r="D34" s="62">
         <v>0.52364381017028427</v>
       </c>
       <c r="E34" s="40"/>
     </row>
     <row r="35" spans="1:5" ht="3" customHeight="1">
       <c r="A35" s="40"/>
-      <c r="B35" s="65"/>
+      <c r="B35" s="58"/>
       <c r="C35" s="33"/>
-      <c r="D35" s="66"/>
+      <c r="D35" s="59"/>
       <c r="E35" s="40"/>
     </row>
     <row r="36" spans="1:5" ht="23" customHeight="1">
       <c r="A36" s="40"/>
-      <c r="B36" s="70" t="s">
+      <c r="B36" s="63" t="s">
         <v>32</v>
       </c>
-      <c r="C36" s="71">
+      <c r="C36" s="64">
         <v>7.3904497600149111E-2</v>
       </c>
-      <c r="D36" s="72">
+      <c r="D36" s="65">
         <v>7.5095139422881152E-2</v>
       </c>
       <c r="E36" s="40"/>
@@ -18329,7 +18356,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C6:D30">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -18342,51 +18369,51 @@
   <dimension ref="A1:S55"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="12" width="10.83203125" style="44"/>
+    <col min="2" max="12" width="10.83203125" style="43"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19">
       <c r="A1" s="40"/>
-      <c r="B1" s="49">
+      <c r="B1" s="48">
         <v>0.01</v>
       </c>
-      <c r="C1" s="49">
+      <c r="C1" s="48">
         <f>B1+0.5%</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="D1" s="49">
+      <c r="D1" s="48">
         <f t="shared" ref="D1:L1" si="0">C1+0.5%</f>
         <v>0.02</v>
       </c>
-      <c r="E1" s="49">
+      <c r="E1" s="48">
         <f t="shared" si="0"/>
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="F1" s="49">
+      <c r="F1" s="48">
         <f t="shared" si="0"/>
         <v>3.0000000000000002E-2</v>
       </c>
-      <c r="G1" s="49">
+      <c r="G1" s="48">
         <f t="shared" si="0"/>
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="H1" s="49">
+      <c r="H1" s="48">
         <f t="shared" si="0"/>
         <v>0.04</v>
       </c>
-      <c r="I1" s="49">
+      <c r="I1" s="48">
         <f t="shared" si="0"/>
         <v>4.4999999999999998E-2</v>
       </c>
-      <c r="J1" s="49">
+      <c r="J1" s="48">
         <f t="shared" si="0"/>
         <v>4.9999999999999996E-2</v>
       </c>
-      <c r="K1" s="49">
+      <c r="K1" s="48">
         <f t="shared" si="0"/>
         <v>5.4999999999999993E-2</v>
       </c>
-      <c r="L1" s="49">
+      <c r="L1" s="48">
         <f t="shared" si="0"/>
         <v>5.9999999999999991E-2</v>
       </c>
@@ -18400,37 +18427,37 @@
     </row>
     <row r="2" spans="1:19">
       <c r="A2" s="40"/>
-      <c r="B2" s="45" t="s">
+      <c r="B2" s="44" t="s">
         <v>129</v>
       </c>
-      <c r="C2" s="45" t="s">
+      <c r="C2" s="44" t="s">
         <v>130</v>
       </c>
-      <c r="D2" s="45" t="s">
+      <c r="D2" s="44" t="s">
         <v>131</v>
       </c>
-      <c r="E2" s="45" t="s">
+      <c r="E2" s="44" t="s">
         <v>132</v>
       </c>
-      <c r="F2" s="45" t="s">
+      <c r="F2" s="44" t="s">
         <v>133</v>
       </c>
-      <c r="G2" s="45" t="s">
+      <c r="G2" s="44" t="s">
         <v>134</v>
       </c>
-      <c r="H2" s="45" t="s">
+      <c r="H2" s="44" t="s">
         <v>135</v>
       </c>
-      <c r="I2" s="45" t="s">
+      <c r="I2" s="44" t="s">
         <v>136</v>
       </c>
-      <c r="J2" s="45" t="s">
+      <c r="J2" s="44" t="s">
         <v>137</v>
       </c>
-      <c r="K2" s="45" t="s">
+      <c r="K2" s="44" t="s">
         <v>138</v>
       </c>
-      <c r="L2" s="45" t="s">
+      <c r="L2" s="44" t="s">
         <v>139</v>
       </c>
       <c r="M2" s="40"/>
@@ -18445,37 +18472,37 @@
       <c r="A3" s="40">
         <v>0</v>
       </c>
-      <c r="B3" s="45">
+      <c r="B3" s="44">
         <v>1</v>
       </c>
-      <c r="C3" s="45">
+      <c r="C3" s="44">
         <v>1</v>
       </c>
-      <c r="D3" s="45">
+      <c r="D3" s="44">
         <v>1</v>
       </c>
-      <c r="E3" s="45">
+      <c r="E3" s="44">
         <v>1</v>
       </c>
-      <c r="F3" s="45">
+      <c r="F3" s="44">
         <v>1</v>
       </c>
-      <c r="G3" s="45">
+      <c r="G3" s="44">
         <v>1</v>
       </c>
-      <c r="H3" s="45">
+      <c r="H3" s="44">
         <v>1</v>
       </c>
-      <c r="I3" s="45">
+      <c r="I3" s="44">
         <v>1</v>
       </c>
-      <c r="J3" s="45">
+      <c r="J3" s="44">
         <v>1</v>
       </c>
-      <c r="K3" s="45">
+      <c r="K3" s="44">
         <v>1</v>
       </c>
-      <c r="L3" s="45">
+      <c r="L3" s="44">
         <v>1</v>
       </c>
       <c r="M3" s="40"/>
@@ -18490,37 +18517,37 @@
       <c r="A4" s="40">
         <v>1</v>
       </c>
-      <c r="B4" s="45">
+      <c r="B4" s="44">
         <v>0.73380000000000001</v>
       </c>
-      <c r="C4" s="45">
+      <c r="C4" s="44">
         <v>0.71775</v>
       </c>
-      <c r="D4" s="45">
+      <c r="D4" s="44">
         <v>0.69374999999999998</v>
       </c>
-      <c r="E4" s="45">
+      <c r="E4" s="44">
         <v>0.67395000000000005</v>
       </c>
-      <c r="F4" s="45">
+      <c r="F4" s="44">
         <v>0.66169999999999995</v>
       </c>
-      <c r="G4" s="45">
+      <c r="G4" s="44">
         <v>0.64059999999999995</v>
       </c>
-      <c r="H4" s="45">
+      <c r="H4" s="44">
         <v>0.61555000000000004</v>
       </c>
-      <c r="I4" s="45">
+      <c r="I4" s="44">
         <v>0.6</v>
       </c>
-      <c r="J4" s="45">
+      <c r="J4" s="44">
         <v>0.57394999999999996</v>
       </c>
-      <c r="K4" s="45">
+      <c r="K4" s="44">
         <v>0.54879999999999995</v>
       </c>
-      <c r="L4" s="45">
+      <c r="L4" s="44">
         <v>0.51765000000000005</v>
       </c>
       <c r="M4" s="40"/>
@@ -18535,37 +18562,37 @@
       <c r="A5" s="40">
         <v>2</v>
       </c>
-      <c r="B5" s="45">
+      <c r="B5" s="44">
         <v>0.79205000000000003</v>
       </c>
-      <c r="C5" s="45">
+      <c r="C5" s="44">
         <v>0.76585000000000003</v>
       </c>
-      <c r="D5" s="45">
+      <c r="D5" s="44">
         <v>0.73955000000000004</v>
       </c>
-      <c r="E5" s="45">
+      <c r="E5" s="44">
         <v>0.71504999999999996</v>
       </c>
-      <c r="F5" s="45">
+      <c r="F5" s="44">
         <v>0.68979999999999997</v>
       </c>
-      <c r="G5" s="45">
+      <c r="G5" s="44">
         <v>0.65825</v>
       </c>
-      <c r="H5" s="45">
+      <c r="H5" s="44">
         <v>0.62665000000000004</v>
       </c>
-      <c r="I5" s="45">
+      <c r="I5" s="44">
         <v>0.59260000000000002</v>
       </c>
-      <c r="J5" s="45">
+      <c r="J5" s="44">
         <v>0.56069999999999998</v>
       </c>
-      <c r="K5" s="45">
+      <c r="K5" s="44">
         <v>0.52849999999999997</v>
       </c>
-      <c r="L5" s="45">
+      <c r="L5" s="44">
         <v>0.49690000000000001</v>
       </c>
       <c r="M5" s="40"/>
@@ -18580,37 +18607,37 @@
       <c r="A6" s="40">
         <v>3</v>
       </c>
-      <c r="B6" s="45">
+      <c r="B6" s="44">
         <v>0.84904999999999997</v>
       </c>
-      <c r="C6" s="45">
+      <c r="C6" s="44">
         <v>0.82</v>
       </c>
-      <c r="D6" s="45">
+      <c r="D6" s="44">
         <v>0.79064999999999996</v>
       </c>
-      <c r="E6" s="45">
+      <c r="E6" s="44">
         <v>0.75814999999999999</v>
       </c>
-      <c r="F6" s="45">
+      <c r="F6" s="44">
         <v>0.71840000000000004</v>
       </c>
-      <c r="G6" s="45">
+      <c r="G6" s="44">
         <v>0.67674999999999996</v>
       </c>
-      <c r="H6" s="45">
+      <c r="H6" s="44">
         <v>0.64090000000000003</v>
       </c>
-      <c r="I6" s="45">
+      <c r="I6" s="44">
         <v>0.59755000000000003</v>
       </c>
-      <c r="J6" s="45">
+      <c r="J6" s="44">
         <v>0.55264999999999997</v>
       </c>
-      <c r="K6" s="45">
+      <c r="K6" s="44">
         <v>0.50900000000000001</v>
       </c>
-      <c r="L6" s="45">
+      <c r="L6" s="44">
         <v>0.46315000000000001</v>
       </c>
       <c r="M6" s="40"/>
@@ -18625,37 +18652,37 @@
       <c r="A7" s="40">
         <v>4</v>
       </c>
-      <c r="B7" s="45">
+      <c r="B7" s="44">
         <v>0.87555000000000005</v>
       </c>
-      <c r="C7" s="45">
+      <c r="C7" s="44">
         <v>0.84814999999999996</v>
       </c>
-      <c r="D7" s="45">
+      <c r="D7" s="44">
         <v>0.8175</v>
       </c>
-      <c r="E7" s="45">
+      <c r="E7" s="44">
         <v>0.7833</v>
       </c>
-      <c r="F7" s="45">
+      <c r="F7" s="44">
         <v>0.74345000000000006</v>
       </c>
-      <c r="G7" s="45">
+      <c r="G7" s="44">
         <v>0.70179999999999998</v>
       </c>
-      <c r="H7" s="45">
+      <c r="H7" s="44">
         <v>0.65710000000000002</v>
       </c>
-      <c r="I7" s="45">
+      <c r="I7" s="44">
         <v>0.60675000000000001</v>
       </c>
-      <c r="J7" s="45">
+      <c r="J7" s="44">
         <v>0.55600000000000005</v>
       </c>
-      <c r="K7" s="45">
+      <c r="K7" s="44">
         <v>0.50234999999999996</v>
       </c>
-      <c r="L7" s="45">
+      <c r="L7" s="44">
         <v>0.45315</v>
       </c>
       <c r="M7" s="40"/>
@@ -18670,37 +18697,37 @@
       <c r="A8" s="40">
         <v>5</v>
       </c>
-      <c r="B8" s="42">
+      <c r="B8" s="41">
         <v>0.89715</v>
       </c>
-      <c r="C8" s="42">
+      <c r="C8" s="41">
         <v>0.87119999999999997</v>
       </c>
-      <c r="D8" s="42">
+      <c r="D8" s="41">
         <v>0.84065000000000001</v>
       </c>
-      <c r="E8" s="42">
+      <c r="E8" s="41">
         <v>0.80395000000000005</v>
       </c>
-      <c r="F8" s="42">
+      <c r="F8" s="41">
         <v>0.76329999999999998</v>
       </c>
-      <c r="G8" s="42">
+      <c r="G8" s="41">
         <v>0.72004999999999997</v>
       </c>
-      <c r="H8" s="42">
+      <c r="H8" s="41">
         <v>0.67290000000000005</v>
       </c>
-      <c r="I8" s="42">
+      <c r="I8" s="41">
         <v>0.61814999999999998</v>
       </c>
-      <c r="J8" s="42">
+      <c r="J8" s="41">
         <v>0.56084999999999996</v>
       </c>
-      <c r="K8" s="42">
+      <c r="K8" s="41">
         <v>0.50544999999999995</v>
       </c>
-      <c r="L8" s="42">
+      <c r="L8" s="41">
         <v>0.4451</v>
       </c>
       <c r="M8" s="40"/>
@@ -18715,37 +18742,37 @@
       <c r="A9" s="40">
         <v>6</v>
       </c>
-      <c r="B9" s="42">
+      <c r="B9" s="41">
         <v>0.91385000000000005</v>
       </c>
-      <c r="C9" s="42">
+      <c r="C9" s="41">
         <v>0.88895000000000002</v>
       </c>
-      <c r="D9" s="42">
+      <c r="D9" s="41">
         <v>0.85870000000000002</v>
       </c>
-      <c r="E9" s="42">
+      <c r="E9" s="41">
         <v>0.82135000000000002</v>
       </c>
-      <c r="F9" s="42">
+      <c r="F9" s="41">
         <v>0.78010000000000002</v>
       </c>
-      <c r="G9" s="42">
+      <c r="G9" s="41">
         <v>0.73199999999999998</v>
       </c>
-      <c r="H9" s="42">
+      <c r="H9" s="41">
         <v>0.68145</v>
       </c>
-      <c r="I9" s="42">
+      <c r="I9" s="41">
         <v>0.62424999999999997</v>
       </c>
-      <c r="J9" s="42">
+      <c r="J9" s="41">
         <v>0.5625</v>
       </c>
-      <c r="K9" s="42">
+      <c r="K9" s="41">
         <v>0.50224999999999997</v>
       </c>
-      <c r="L9" s="42">
+      <c r="L9" s="41">
         <v>0.437</v>
       </c>
       <c r="M9" s="40"/>
@@ -18760,37 +18787,37 @@
       <c r="A10" s="40">
         <v>7</v>
       </c>
-      <c r="B10" s="42">
+      <c r="B10" s="41">
         <v>0.91715000000000002</v>
       </c>
-      <c r="C10" s="42">
+      <c r="C10" s="41">
         <v>0.89529999999999998</v>
       </c>
-      <c r="D10" s="42">
+      <c r="D10" s="41">
         <v>0.8639</v>
       </c>
-      <c r="E10" s="42">
+      <c r="E10" s="41">
         <v>0.82835000000000003</v>
       </c>
-      <c r="F10" s="42">
+      <c r="F10" s="41">
         <v>0.78564999999999996</v>
       </c>
-      <c r="G10" s="42">
+      <c r="G10" s="41">
         <v>0.73619999999999997</v>
       </c>
-      <c r="H10" s="42">
+      <c r="H10" s="41">
         <v>0.68074999999999997</v>
       </c>
-      <c r="I10" s="42">
+      <c r="I10" s="41">
         <v>0.62434999999999996</v>
       </c>
-      <c r="J10" s="42">
+      <c r="J10" s="41">
         <v>0.55764999999999998</v>
       </c>
-      <c r="K10" s="42">
+      <c r="K10" s="41">
         <v>0.49530000000000002</v>
       </c>
-      <c r="L10" s="42">
+      <c r="L10" s="41">
         <v>0.42995</v>
       </c>
       <c r="M10" s="40"/>
@@ -18805,37 +18832,37 @@
       <c r="A11" s="40">
         <v>8</v>
       </c>
-      <c r="B11" s="42">
+      <c r="B11" s="41">
         <v>0.92290000000000005</v>
       </c>
-      <c r="C11" s="42">
+      <c r="C11" s="41">
         <v>0.89880000000000004</v>
       </c>
-      <c r="D11" s="42">
+      <c r="D11" s="41">
         <v>0.86839999999999995</v>
       </c>
-      <c r="E11" s="42">
+      <c r="E11" s="41">
         <v>0.83245000000000002</v>
       </c>
-      <c r="F11" s="42">
+      <c r="F11" s="41">
         <v>0.78644999999999998</v>
       </c>
-      <c r="G11" s="42">
+      <c r="G11" s="41">
         <v>0.73609999999999998</v>
       </c>
-      <c r="H11" s="42">
+      <c r="H11" s="41">
         <v>0.67964999999999998</v>
       </c>
-      <c r="I11" s="42">
+      <c r="I11" s="41">
         <v>0.61980000000000002</v>
       </c>
-      <c r="J11" s="42">
+      <c r="J11" s="41">
         <v>0.55264999999999997</v>
       </c>
-      <c r="K11" s="42">
+      <c r="K11" s="41">
         <v>0.48230000000000001</v>
       </c>
-      <c r="L11" s="42">
+      <c r="L11" s="41">
         <v>0.41360000000000002</v>
       </c>
       <c r="M11" s="40"/>
@@ -18850,37 +18877,37 @@
       <c r="A12" s="40">
         <v>9</v>
       </c>
-      <c r="B12" s="42">
+      <c r="B12" s="41">
         <v>0.92554999999999998</v>
       </c>
-      <c r="C12" s="42">
+      <c r="C12" s="41">
         <v>0.9</v>
       </c>
-      <c r="D12" s="42">
+      <c r="D12" s="41">
         <v>0.86939999999999995</v>
       </c>
-      <c r="E12" s="42">
+      <c r="E12" s="41">
         <v>0.83365</v>
       </c>
-      <c r="F12" s="42">
+      <c r="F12" s="41">
         <v>0.78910000000000002</v>
       </c>
-      <c r="G12" s="42">
+      <c r="G12" s="41">
         <v>0.73645000000000005</v>
       </c>
-      <c r="H12" s="42">
+      <c r="H12" s="41">
         <v>0.67625000000000002</v>
       </c>
-      <c r="I12" s="42">
+      <c r="I12" s="41">
         <v>0.61114999999999997</v>
       </c>
-      <c r="J12" s="42">
+      <c r="J12" s="41">
         <v>0.54379999999999995</v>
       </c>
-      <c r="K12" s="42">
+      <c r="K12" s="41">
         <v>0.47089999999999999</v>
       </c>
-      <c r="L12" s="42">
+      <c r="L12" s="41">
         <v>0.39555000000000001</v>
       </c>
       <c r="M12" s="40"/>
@@ -18895,37 +18922,37 @@
       <c r="A13" s="40">
         <v>10</v>
       </c>
-      <c r="B13" s="42">
+      <c r="B13" s="41">
         <v>0.93115000000000003</v>
       </c>
-      <c r="C13" s="42">
+      <c r="C13" s="41">
         <v>0.90690000000000004</v>
       </c>
-      <c r="D13" s="42">
+      <c r="D13" s="41">
         <v>0.87309999999999999</v>
       </c>
-      <c r="E13" s="42">
+      <c r="E13" s="41">
         <v>0.83379999999999999</v>
       </c>
-      <c r="F13" s="42">
+      <c r="F13" s="41">
         <v>0.78664999999999996</v>
       </c>
-      <c r="G13" s="42">
+      <c r="G13" s="41">
         <v>0.73399999999999999</v>
       </c>
-      <c r="H13" s="42">
+      <c r="H13" s="41">
         <v>0.67225000000000001</v>
       </c>
-      <c r="I13" s="42">
+      <c r="I13" s="41">
         <v>0.60235000000000005</v>
       </c>
-      <c r="J13" s="42">
+      <c r="J13" s="41">
         <v>0.53005000000000002</v>
       </c>
-      <c r="K13" s="42">
+      <c r="K13" s="41">
         <v>0.45765</v>
       </c>
-      <c r="L13" s="42">
+      <c r="L13" s="41">
         <v>0.38114999999999999</v>
       </c>
       <c r="M13" s="40"/>
@@ -18940,37 +18967,37 @@
       <c r="A14" s="40">
         <v>11</v>
       </c>
-      <c r="B14" s="42">
+      <c r="B14" s="41">
         <v>0.93400000000000005</v>
       </c>
-      <c r="C14" s="42">
+      <c r="C14" s="41">
         <v>0.90890000000000004</v>
       </c>
-      <c r="D14" s="42">
+      <c r="D14" s="41">
         <v>0.87450000000000006</v>
       </c>
-      <c r="E14" s="42">
+      <c r="E14" s="41">
         <v>0.83284999999999998</v>
       </c>
-      <c r="F14" s="42">
+      <c r="F14" s="41">
         <v>0.78559999999999997</v>
       </c>
-      <c r="G14" s="42">
+      <c r="G14" s="41">
         <v>0.73070000000000002</v>
       </c>
-      <c r="H14" s="42">
+      <c r="H14" s="41">
         <v>0.66769999999999996</v>
       </c>
-      <c r="I14" s="42">
+      <c r="I14" s="41">
         <v>0.59755000000000003</v>
       </c>
-      <c r="J14" s="42">
+      <c r="J14" s="41">
         <v>0.51885000000000003</v>
       </c>
-      <c r="K14" s="42">
+      <c r="K14" s="41">
         <v>0.4405</v>
       </c>
-      <c r="L14" s="42">
+      <c r="L14" s="41">
         <v>0.36770000000000003</v>
       </c>
       <c r="M14" s="40"/>
@@ -18985,37 +19012,37 @@
       <c r="A15" s="40">
         <v>12</v>
       </c>
-      <c r="B15" s="42">
+      <c r="B15" s="41">
         <v>0.93630000000000002</v>
       </c>
-      <c r="C15" s="42">
+      <c r="C15" s="41">
         <v>0.91034999999999999</v>
       </c>
-      <c r="D15" s="42">
+      <c r="D15" s="41">
         <v>0.877</v>
       </c>
-      <c r="E15" s="42">
+      <c r="E15" s="41">
         <v>0.83684999999999998</v>
       </c>
-      <c r="F15" s="42">
+      <c r="F15" s="41">
         <v>0.78939999999999999</v>
       </c>
-      <c r="G15" s="42">
+      <c r="G15" s="41">
         <v>0.73085</v>
       </c>
-      <c r="H15" s="42">
+      <c r="H15" s="41">
         <v>0.66225000000000001</v>
       </c>
-      <c r="I15" s="42">
+      <c r="I15" s="41">
         <v>0.59075</v>
       </c>
-      <c r="J15" s="42">
+      <c r="J15" s="41">
         <v>0.50965000000000005</v>
       </c>
-      <c r="K15" s="42">
+      <c r="K15" s="41">
         <v>0.43045</v>
       </c>
-      <c r="L15" s="42">
+      <c r="L15" s="41">
         <v>0.35439999999999999</v>
       </c>
       <c r="M15" s="40"/>
@@ -19030,37 +19057,37 @@
       <c r="A16" s="40">
         <v>13</v>
       </c>
-      <c r="B16" s="42">
+      <c r="B16" s="41">
         <v>0.93874999999999997</v>
       </c>
-      <c r="C16" s="42">
+      <c r="C16" s="41">
         <v>0.91290000000000004</v>
       </c>
-      <c r="D16" s="42">
+      <c r="D16" s="41">
         <v>0.87944999999999995</v>
       </c>
-      <c r="E16" s="42">
+      <c r="E16" s="41">
         <v>0.83714999999999995</v>
       </c>
-      <c r="F16" s="42">
+      <c r="F16" s="41">
         <v>0.78715000000000002</v>
       </c>
-      <c r="G16" s="42">
+      <c r="G16" s="41">
         <v>0.72914999999999996</v>
       </c>
-      <c r="H16" s="42">
+      <c r="H16" s="41">
         <v>0.65880000000000005</v>
       </c>
-      <c r="I16" s="42">
+      <c r="I16" s="41">
         <v>0.5847</v>
       </c>
-      <c r="J16" s="42">
+      <c r="J16" s="41">
         <v>0.50280000000000002</v>
       </c>
-      <c r="K16" s="42">
+      <c r="K16" s="41">
         <v>0.42049999999999998</v>
       </c>
-      <c r="L16" s="42">
+      <c r="L16" s="41">
         <v>0.34515000000000001</v>
       </c>
       <c r="M16" s="40"/>
@@ -19075,37 +19102,37 @@
       <c r="A17" s="40">
         <v>14</v>
       </c>
-      <c r="B17" s="42">
+      <c r="B17" s="41">
         <v>0.94084999999999996</v>
       </c>
-      <c r="C17" s="42">
+      <c r="C17" s="41">
         <v>0.91644999999999999</v>
       </c>
-      <c r="D17" s="42">
+      <c r="D17" s="41">
         <v>0.88360000000000005</v>
       </c>
-      <c r="E17" s="42">
+      <c r="E17" s="41">
         <v>0.84204999999999997</v>
       </c>
-      <c r="F17" s="42">
+      <c r="F17" s="41">
         <v>0.78805000000000003</v>
       </c>
-      <c r="G17" s="42">
+      <c r="G17" s="41">
         <v>0.72655000000000003</v>
       </c>
-      <c r="H17" s="42">
+      <c r="H17" s="41">
         <v>0.65664999999999996</v>
       </c>
-      <c r="I17" s="42">
+      <c r="I17" s="41">
         <v>0.58125000000000004</v>
       </c>
-      <c r="J17" s="42">
+      <c r="J17" s="41">
         <v>0.49690000000000001</v>
       </c>
-      <c r="K17" s="42">
+      <c r="K17" s="41">
         <v>0.41184999999999999</v>
       </c>
-      <c r="L17" s="42">
+      <c r="L17" s="41">
         <v>0.3342</v>
       </c>
       <c r="M17" s="40"/>
@@ -19120,37 +19147,37 @@
       <c r="A18" s="40">
         <v>15</v>
       </c>
-      <c r="B18" s="42">
+      <c r="B18" s="41">
         <v>0.94489999999999996</v>
       </c>
-      <c r="C18" s="42">
+      <c r="C18" s="41">
         <v>0.91930000000000001</v>
       </c>
-      <c r="D18" s="42">
+      <c r="D18" s="41">
         <v>0.88639999999999997</v>
       </c>
-      <c r="E18" s="42">
+      <c r="E18" s="41">
         <v>0.84330000000000005</v>
       </c>
-      <c r="F18" s="42">
+      <c r="F18" s="41">
         <v>0.78985000000000005</v>
       </c>
-      <c r="G18" s="42">
+      <c r="G18" s="41">
         <v>0.72499999999999998</v>
       </c>
-      <c r="H18" s="42">
+      <c r="H18" s="41">
         <v>0.65359999999999996</v>
       </c>
-      <c r="I18" s="42">
+      <c r="I18" s="41">
         <v>0.57694999999999996</v>
       </c>
-      <c r="J18" s="42">
+      <c r="J18" s="41">
         <v>0.48845</v>
       </c>
-      <c r="K18" s="42">
+      <c r="K18" s="41">
         <v>0.40200000000000002</v>
       </c>
-      <c r="L18" s="42">
+      <c r="L18" s="41">
         <v>0.32450000000000001</v>
       </c>
       <c r="M18" s="40"/>
@@ -19165,37 +19192,37 @@
       <c r="A19" s="40">
         <v>16</v>
       </c>
-      <c r="B19" s="42">
+      <c r="B19" s="41">
         <v>0.94664999999999999</v>
       </c>
-      <c r="C19" s="42">
+      <c r="C19" s="41">
         <v>0.92210000000000003</v>
       </c>
-      <c r="D19" s="42">
+      <c r="D19" s="41">
         <v>0.8891</v>
       </c>
-      <c r="E19" s="42">
+      <c r="E19" s="41">
         <v>0.84684999999999999</v>
       </c>
-      <c r="F19" s="42">
+      <c r="F19" s="41">
         <v>0.79179999999999995</v>
       </c>
-      <c r="G19" s="42">
+      <c r="G19" s="41">
         <v>0.7238</v>
       </c>
-      <c r="H19" s="42">
+      <c r="H19" s="41">
         <v>0.65154999999999996</v>
       </c>
-      <c r="I19" s="42">
+      <c r="I19" s="41">
         <v>0.57220000000000004</v>
       </c>
-      <c r="J19" s="42">
+      <c r="J19" s="41">
         <v>0.48449999999999999</v>
       </c>
-      <c r="K19" s="42">
+      <c r="K19" s="41">
         <v>0.39529999999999998</v>
       </c>
-      <c r="L19" s="42">
+      <c r="L19" s="41">
         <v>0.31659999999999999</v>
       </c>
       <c r="M19" s="40"/>
@@ -19210,37 +19237,37 @@
       <c r="A20" s="40">
         <v>17</v>
       </c>
-      <c r="B20" s="42">
+      <c r="B20" s="41">
         <v>0.94864999999999999</v>
       </c>
-      <c r="C20" s="42">
+      <c r="C20" s="41">
         <v>0.92374999999999996</v>
       </c>
-      <c r="D20" s="42">
+      <c r="D20" s="41">
         <v>0.89205000000000001</v>
       </c>
-      <c r="E20" s="42">
+      <c r="E20" s="41">
         <v>0.84730000000000005</v>
       </c>
-      <c r="F20" s="42">
+      <c r="F20" s="41">
         <v>0.79149999999999998</v>
       </c>
-      <c r="G20" s="42">
+      <c r="G20" s="41">
         <v>0.72504999999999997</v>
       </c>
-      <c r="H20" s="42">
+      <c r="H20" s="41">
         <v>0.64834999999999998</v>
       </c>
-      <c r="I20" s="42">
+      <c r="I20" s="41">
         <v>0.56545000000000001</v>
       </c>
-      <c r="J20" s="42">
+      <c r="J20" s="41">
         <v>0.47825000000000001</v>
       </c>
-      <c r="K20" s="42">
+      <c r="K20" s="41">
         <v>0.39024999999999999</v>
       </c>
-      <c r="L20" s="42">
+      <c r="L20" s="41">
         <v>0.30795</v>
       </c>
       <c r="M20" s="40"/>
@@ -19255,37 +19282,37 @@
       <c r="A21" s="40">
         <v>18</v>
       </c>
-      <c r="B21" s="42">
+      <c r="B21" s="41">
         <v>0.95125000000000004</v>
       </c>
-      <c r="C21" s="42">
+      <c r="C21" s="41">
         <v>0.92635000000000001</v>
       </c>
-      <c r="D21" s="42">
+      <c r="D21" s="41">
         <v>0.89400000000000002</v>
       </c>
-      <c r="E21" s="42">
+      <c r="E21" s="41">
         <v>0.84835000000000005</v>
       </c>
-      <c r="F21" s="42">
+      <c r="F21" s="41">
         <v>0.79374999999999996</v>
       </c>
-      <c r="G21" s="42">
+      <c r="G21" s="41">
         <v>0.72430000000000005</v>
       </c>
-      <c r="H21" s="42">
+      <c r="H21" s="41">
         <v>0.64754999999999996</v>
       </c>
-      <c r="I21" s="42">
+      <c r="I21" s="41">
         <v>0.56379999999999997</v>
       </c>
-      <c r="J21" s="42">
+      <c r="J21" s="41">
         <v>0.47344999999999998</v>
       </c>
-      <c r="K21" s="42">
+      <c r="K21" s="41">
         <v>0.38405</v>
       </c>
-      <c r="L21" s="42">
+      <c r="L21" s="41">
         <v>0.30170000000000002</v>
       </c>
       <c r="M21" s="40"/>
@@ -19300,37 +19327,37 @@
       <c r="A22" s="40">
         <v>19</v>
       </c>
-      <c r="B22" s="42">
+      <c r="B22" s="41">
         <v>0.95399999999999996</v>
       </c>
-      <c r="C22" s="42">
+      <c r="C22" s="41">
         <v>0.9294</v>
       </c>
-      <c r="D22" s="42">
+      <c r="D22" s="41">
         <v>0.89615</v>
       </c>
-      <c r="E22" s="42">
+      <c r="E22" s="41">
         <v>0.85109999999999997</v>
       </c>
-      <c r="F22" s="42">
+      <c r="F22" s="41">
         <v>0.79520000000000002</v>
       </c>
-      <c r="G22" s="42">
+      <c r="G22" s="41">
         <v>0.72445000000000004</v>
       </c>
-      <c r="H22" s="42">
+      <c r="H22" s="41">
         <v>0.64590000000000003</v>
       </c>
-      <c r="I22" s="42">
+      <c r="I22" s="41">
         <v>0.55915000000000004</v>
       </c>
-      <c r="J22" s="42">
+      <c r="J22" s="41">
         <v>0.4703</v>
       </c>
-      <c r="K22" s="42">
+      <c r="K22" s="41">
         <v>0.37919999999999998</v>
       </c>
-      <c r="L22" s="42">
+      <c r="L22" s="41">
         <v>0.29415000000000002</v>
       </c>
       <c r="M22" s="40"/>
@@ -19345,37 +19372,37 @@
       <c r="A23" s="40">
         <v>20</v>
       </c>
-      <c r="B23" s="42">
+      <c r="B23" s="41">
         <v>0.95694999999999997</v>
       </c>
-      <c r="C23" s="42">
+      <c r="C23" s="41">
         <v>0.93169999999999997</v>
       </c>
-      <c r="D23" s="42">
+      <c r="D23" s="41">
         <v>0.89949999999999997</v>
       </c>
-      <c r="E23" s="42">
+      <c r="E23" s="41">
         <v>0.85399999999999998</v>
       </c>
-      <c r="F23" s="42">
+      <c r="F23" s="41">
         <v>0.79774999999999996</v>
       </c>
-      <c r="G23" s="42">
+      <c r="G23" s="41">
         <v>0.72529999999999994</v>
       </c>
-      <c r="H23" s="42">
+      <c r="H23" s="41">
         <v>0.64480000000000004</v>
       </c>
-      <c r="I23" s="42">
+      <c r="I23" s="41">
         <v>0.55700000000000005</v>
       </c>
-      <c r="J23" s="42">
+      <c r="J23" s="41">
         <v>0.46465000000000001</v>
       </c>
-      <c r="K23" s="42">
+      <c r="K23" s="41">
         <v>0.373</v>
       </c>
-      <c r="L23" s="42">
+      <c r="L23" s="41">
         <v>0.28820000000000001</v>
       </c>
       <c r="M23" s="40"/>
@@ -19388,47 +19415,47 @@
     </row>
     <row r="24" spans="1:19">
       <c r="A24" s="40"/>
-      <c r="B24" s="49">
+      <c r="B24" s="48">
         <f>B48</f>
         <v>0</v>
       </c>
-      <c r="C24" s="49">
+      <c r="C24" s="48">
         <f t="shared" ref="C24:L24" si="1">C48</f>
         <v>0</v>
       </c>
-      <c r="D24" s="49">
+      <c r="D24" s="48">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="E24" s="49">
+      <c r="E24" s="48">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F24" s="49">
+      <c r="F24" s="48">
         <f t="shared" si="1"/>
         <v>4.9999999999994398E-5</v>
       </c>
-      <c r="G24" s="49">
+      <c r="G24" s="48">
         <f t="shared" si="1"/>
         <v>9.9999999999988905E-5</v>
       </c>
-      <c r="H24" s="49">
+      <c r="H24" s="48">
         <f t="shared" si="1"/>
         <v>9.5000000000000596E-4</v>
       </c>
-      <c r="I24" s="49">
+      <c r="I24" s="48">
         <f t="shared" si="1"/>
         <v>4.9500000000000099E-3</v>
       </c>
-      <c r="J24" s="49">
+      <c r="J24" s="48">
         <f t="shared" si="1"/>
         <v>1.495E-2</v>
       </c>
-      <c r="K24" s="49">
+      <c r="K24" s="48">
         <f t="shared" si="1"/>
         <v>3.5449999999999898E-2</v>
       </c>
-      <c r="L24" s="49">
+      <c r="L24" s="48">
         <f t="shared" si="1"/>
         <v>7.4799999999999894E-2</v>
       </c>
@@ -19442,17 +19469,17 @@
     </row>
     <row r="25" spans="1:19">
       <c r="A25" s="40"/>
-      <c r="B25" s="45"/>
-      <c r="C25" s="45"/>
-      <c r="D25" s="45"/>
-      <c r="E25" s="45"/>
-      <c r="F25" s="45"/>
-      <c r="G25" s="45"/>
-      <c r="H25" s="45"/>
-      <c r="I25" s="45"/>
-      <c r="J25" s="45"/>
-      <c r="K25" s="45"/>
-      <c r="L25" s="45"/>
+      <c r="B25" s="44"/>
+      <c r="C25" s="44"/>
+      <c r="D25" s="44"/>
+      <c r="E25" s="44"/>
+      <c r="F25" s="44"/>
+      <c r="G25" s="44"/>
+      <c r="H25" s="44"/>
+      <c r="I25" s="44"/>
+      <c r="J25" s="44"/>
+      <c r="K25" s="44"/>
+      <c r="L25" s="44"/>
       <c r="M25" s="40"/>
       <c r="N25" s="40"/>
       <c r="O25" s="40"/>
@@ -19463,17 +19490,17 @@
     </row>
     <row r="26" spans="1:19">
       <c r="A26" s="40"/>
-      <c r="B26" s="45"/>
-      <c r="C26" s="45"/>
-      <c r="D26" s="45"/>
-      <c r="E26" s="45"/>
-      <c r="F26" s="45"/>
-      <c r="G26" s="45"/>
-      <c r="H26" s="45"/>
-      <c r="I26" s="45"/>
-      <c r="J26" s="45"/>
-      <c r="K26" s="45"/>
-      <c r="L26" s="45"/>
+      <c r="B26" s="44"/>
+      <c r="C26" s="44"/>
+      <c r="D26" s="44"/>
+      <c r="E26" s="44"/>
+      <c r="F26" s="44"/>
+      <c r="G26" s="44"/>
+      <c r="H26" s="44"/>
+      <c r="I26" s="44"/>
+      <c r="J26" s="44"/>
+      <c r="K26" s="44"/>
+      <c r="L26" s="44"/>
       <c r="M26" s="40"/>
       <c r="N26" s="40"/>
       <c r="O26" s="40"/>
@@ -19484,37 +19511,37 @@
     </row>
     <row r="27" spans="1:19">
       <c r="A27" s="40"/>
-      <c r="B27" s="45" t="s">
+      <c r="B27" s="44" t="s">
         <v>129</v>
       </c>
-      <c r="C27" s="45" t="s">
+      <c r="C27" s="44" t="s">
         <v>130</v>
       </c>
-      <c r="D27" s="45" t="s">
+      <c r="D27" s="44" t="s">
         <v>131</v>
       </c>
-      <c r="E27" s="45" t="s">
+      <c r="E27" s="44" t="s">
         <v>132</v>
       </c>
-      <c r="F27" s="45" t="s">
+      <c r="F27" s="44" t="s">
         <v>133</v>
       </c>
-      <c r="G27" s="45" t="s">
+      <c r="G27" s="44" t="s">
         <v>134</v>
       </c>
-      <c r="H27" s="45" t="s">
+      <c r="H27" s="44" t="s">
         <v>135</v>
       </c>
-      <c r="I27" s="45" t="s">
+      <c r="I27" s="44" t="s">
         <v>136</v>
       </c>
-      <c r="J27" s="45" t="s">
+      <c r="J27" s="44" t="s">
         <v>137</v>
       </c>
-      <c r="K27" s="45" t="s">
+      <c r="K27" s="44" t="s">
         <v>138</v>
       </c>
-      <c r="L27" s="45" t="s">
+      <c r="L27" s="44" t="s">
         <v>139</v>
       </c>
       <c r="M27" s="40"/>
@@ -19529,37 +19556,37 @@
       <c r="A28" s="40">
         <v>0</v>
       </c>
-      <c r="B28" s="43">
-        <v>0</v>
-      </c>
-      <c r="C28" s="43">
-        <v>0</v>
-      </c>
-      <c r="D28" s="43">
-        <v>0</v>
-      </c>
-      <c r="E28" s="43">
-        <v>0</v>
-      </c>
-      <c r="F28" s="43">
-        <v>0</v>
-      </c>
-      <c r="G28" s="43">
-        <v>0</v>
-      </c>
-      <c r="H28" s="43">
-        <v>0</v>
-      </c>
-      <c r="I28" s="43">
-        <v>0</v>
-      </c>
-      <c r="J28" s="43">
-        <v>0</v>
-      </c>
-      <c r="K28" s="43">
-        <v>0</v>
-      </c>
-      <c r="L28" s="43">
+      <c r="B28" s="42">
+        <v>0</v>
+      </c>
+      <c r="C28" s="42">
+        <v>0</v>
+      </c>
+      <c r="D28" s="42">
+        <v>0</v>
+      </c>
+      <c r="E28" s="42">
+        <v>0</v>
+      </c>
+      <c r="F28" s="42">
+        <v>0</v>
+      </c>
+      <c r="G28" s="42">
+        <v>0</v>
+      </c>
+      <c r="H28" s="42">
+        <v>0</v>
+      </c>
+      <c r="I28" s="42">
+        <v>0</v>
+      </c>
+      <c r="J28" s="42">
+        <v>0</v>
+      </c>
+      <c r="K28" s="42">
+        <v>0</v>
+      </c>
+      <c r="L28" s="42">
         <v>0</v>
       </c>
       <c r="M28" s="40"/>
@@ -19574,37 +19601,37 @@
       <c r="A29" s="40">
         <v>1</v>
       </c>
-      <c r="B29" s="43">
-        <v>0</v>
-      </c>
-      <c r="C29" s="43">
-        <v>0</v>
-      </c>
-      <c r="D29" s="43">
-        <v>0</v>
-      </c>
-      <c r="E29" s="43">
-        <v>0</v>
-      </c>
-      <c r="F29" s="43">
-        <v>0</v>
-      </c>
-      <c r="G29" s="43">
-        <v>0</v>
-      </c>
-      <c r="H29" s="43">
-        <v>0</v>
-      </c>
-      <c r="I29" s="43">
-        <v>0</v>
-      </c>
-      <c r="J29" s="43">
-        <v>0</v>
-      </c>
-      <c r="K29" s="43">
-        <v>0</v>
-      </c>
-      <c r="L29" s="43">
+      <c r="B29" s="42">
+        <v>0</v>
+      </c>
+      <c r="C29" s="42">
+        <v>0</v>
+      </c>
+      <c r="D29" s="42">
+        <v>0</v>
+      </c>
+      <c r="E29" s="42">
+        <v>0</v>
+      </c>
+      <c r="F29" s="42">
+        <v>0</v>
+      </c>
+      <c r="G29" s="42">
+        <v>0</v>
+      </c>
+      <c r="H29" s="42">
+        <v>0</v>
+      </c>
+      <c r="I29" s="42">
+        <v>0</v>
+      </c>
+      <c r="J29" s="42">
+        <v>0</v>
+      </c>
+      <c r="K29" s="42">
+        <v>0</v>
+      </c>
+      <c r="L29" s="42">
         <v>0</v>
       </c>
       <c r="M29" s="40"/>
@@ -19619,37 +19646,37 @@
       <c r="A30" s="40">
         <v>2</v>
       </c>
-      <c r="B30" s="43">
-        <v>0</v>
-      </c>
-      <c r="C30" s="43">
-        <v>0</v>
-      </c>
-      <c r="D30" s="43">
-        <v>0</v>
-      </c>
-      <c r="E30" s="43">
-        <v>0</v>
-      </c>
-      <c r="F30" s="43">
-        <v>0</v>
-      </c>
-      <c r="G30" s="43">
-        <v>0</v>
-      </c>
-      <c r="H30" s="43">
-        <v>0</v>
-      </c>
-      <c r="I30" s="43">
-        <v>0</v>
-      </c>
-      <c r="J30" s="43">
-        <v>0</v>
-      </c>
-      <c r="K30" s="43">
-        <v>0</v>
-      </c>
-      <c r="L30" s="43">
+      <c r="B30" s="42">
+        <v>0</v>
+      </c>
+      <c r="C30" s="42">
+        <v>0</v>
+      </c>
+      <c r="D30" s="42">
+        <v>0</v>
+      </c>
+      <c r="E30" s="42">
+        <v>0</v>
+      </c>
+      <c r="F30" s="42">
+        <v>0</v>
+      </c>
+      <c r="G30" s="42">
+        <v>0</v>
+      </c>
+      <c r="H30" s="42">
+        <v>0</v>
+      </c>
+      <c r="I30" s="42">
+        <v>0</v>
+      </c>
+      <c r="J30" s="42">
+        <v>0</v>
+      </c>
+      <c r="K30" s="42">
+        <v>0</v>
+      </c>
+      <c r="L30" s="42">
         <v>0</v>
       </c>
       <c r="M30" s="40"/>
@@ -19664,37 +19691,37 @@
       <c r="A31" s="40">
         <v>3</v>
       </c>
-      <c r="B31" s="43">
-        <v>0</v>
-      </c>
-      <c r="C31" s="43">
-        <v>0</v>
-      </c>
-      <c r="D31" s="43">
-        <v>0</v>
-      </c>
-      <c r="E31" s="43">
-        <v>0</v>
-      </c>
-      <c r="F31" s="43">
-        <v>0</v>
-      </c>
-      <c r="G31" s="43">
-        <v>0</v>
-      </c>
-      <c r="H31" s="43">
-        <v>0</v>
-      </c>
-      <c r="I31" s="43">
-        <v>0</v>
-      </c>
-      <c r="J31" s="43">
-        <v>0</v>
-      </c>
-      <c r="K31" s="43">
-        <v>0</v>
-      </c>
-      <c r="L31" s="43">
+      <c r="B31" s="42">
+        <v>0</v>
+      </c>
+      <c r="C31" s="42">
+        <v>0</v>
+      </c>
+      <c r="D31" s="42">
+        <v>0</v>
+      </c>
+      <c r="E31" s="42">
+        <v>0</v>
+      </c>
+      <c r="F31" s="42">
+        <v>0</v>
+      </c>
+      <c r="G31" s="42">
+        <v>0</v>
+      </c>
+      <c r="H31" s="42">
+        <v>0</v>
+      </c>
+      <c r="I31" s="42">
+        <v>0</v>
+      </c>
+      <c r="J31" s="42">
+        <v>0</v>
+      </c>
+      <c r="K31" s="42">
+        <v>0</v>
+      </c>
+      <c r="L31" s="42">
         <v>0</v>
       </c>
       <c r="M31" s="40"/>
@@ -19709,37 +19736,37 @@
       <c r="A32" s="40">
         <v>4</v>
       </c>
-      <c r="B32" s="43">
-        <v>0</v>
-      </c>
-      <c r="C32" s="43">
-        <v>0</v>
-      </c>
-      <c r="D32" s="43">
-        <v>0</v>
-      </c>
-      <c r="E32" s="43">
-        <v>0</v>
-      </c>
-      <c r="F32" s="43">
-        <v>0</v>
-      </c>
-      <c r="G32" s="43">
-        <v>0</v>
-      </c>
-      <c r="H32" s="43">
-        <v>0</v>
-      </c>
-      <c r="I32" s="43">
-        <v>0</v>
-      </c>
-      <c r="J32" s="43">
-        <v>0</v>
-      </c>
-      <c r="K32" s="43">
-        <v>0</v>
-      </c>
-      <c r="L32" s="43">
+      <c r="B32" s="42">
+        <v>0</v>
+      </c>
+      <c r="C32" s="42">
+        <v>0</v>
+      </c>
+      <c r="D32" s="42">
+        <v>0</v>
+      </c>
+      <c r="E32" s="42">
+        <v>0</v>
+      </c>
+      <c r="F32" s="42">
+        <v>0</v>
+      </c>
+      <c r="G32" s="42">
+        <v>0</v>
+      </c>
+      <c r="H32" s="42">
+        <v>0</v>
+      </c>
+      <c r="I32" s="42">
+        <v>0</v>
+      </c>
+      <c r="J32" s="42">
+        <v>0</v>
+      </c>
+      <c r="K32" s="42">
+        <v>0</v>
+      </c>
+      <c r="L32" s="42">
         <v>0</v>
       </c>
       <c r="M32" s="40"/>
@@ -19754,37 +19781,37 @@
       <c r="A33" s="40">
         <v>5</v>
       </c>
-      <c r="B33" s="43">
-        <v>0</v>
-      </c>
-      <c r="C33" s="43">
-        <v>0</v>
-      </c>
-      <c r="D33" s="43">
-        <v>0</v>
-      </c>
-      <c r="E33" s="43">
-        <v>0</v>
-      </c>
-      <c r="F33" s="43">
-        <v>0</v>
-      </c>
-      <c r="G33" s="43">
-        <v>0</v>
-      </c>
-      <c r="H33" s="43">
-        <v>0</v>
-      </c>
-      <c r="I33" s="43">
-        <v>0</v>
-      </c>
-      <c r="J33" s="43">
-        <v>0</v>
-      </c>
-      <c r="K33" s="43">
-        <v>0</v>
-      </c>
-      <c r="L33" s="43">
+      <c r="B33" s="42">
+        <v>0</v>
+      </c>
+      <c r="C33" s="42">
+        <v>0</v>
+      </c>
+      <c r="D33" s="42">
+        <v>0</v>
+      </c>
+      <c r="E33" s="42">
+        <v>0</v>
+      </c>
+      <c r="F33" s="42">
+        <v>0</v>
+      </c>
+      <c r="G33" s="42">
+        <v>0</v>
+      </c>
+      <c r="H33" s="42">
+        <v>0</v>
+      </c>
+      <c r="I33" s="42">
+        <v>0</v>
+      </c>
+      <c r="J33" s="42">
+        <v>0</v>
+      </c>
+      <c r="K33" s="42">
+        <v>0</v>
+      </c>
+      <c r="L33" s="42">
         <v>0</v>
       </c>
       <c r="M33" s="40"/>
@@ -19799,37 +19826,37 @@
       <c r="A34" s="40">
         <v>6</v>
       </c>
-      <c r="B34" s="43">
-        <v>0</v>
-      </c>
-      <c r="C34" s="43">
-        <v>0</v>
-      </c>
-      <c r="D34" s="43">
-        <v>0</v>
-      </c>
-      <c r="E34" s="43">
-        <v>0</v>
-      </c>
-      <c r="F34" s="43">
-        <v>0</v>
-      </c>
-      <c r="G34" s="43">
-        <v>0</v>
-      </c>
-      <c r="H34" s="43">
-        <v>0</v>
-      </c>
-      <c r="I34" s="43">
-        <v>0</v>
-      </c>
-      <c r="J34" s="43">
-        <v>0</v>
-      </c>
-      <c r="K34" s="43">
-        <v>0</v>
-      </c>
-      <c r="L34" s="43">
+      <c r="B34" s="42">
+        <v>0</v>
+      </c>
+      <c r="C34" s="42">
+        <v>0</v>
+      </c>
+      <c r="D34" s="42">
+        <v>0</v>
+      </c>
+      <c r="E34" s="42">
+        <v>0</v>
+      </c>
+      <c r="F34" s="42">
+        <v>0</v>
+      </c>
+      <c r="G34" s="42">
+        <v>0</v>
+      </c>
+      <c r="H34" s="42">
+        <v>0</v>
+      </c>
+      <c r="I34" s="42">
+        <v>0</v>
+      </c>
+      <c r="J34" s="42">
+        <v>0</v>
+      </c>
+      <c r="K34" s="42">
+        <v>0</v>
+      </c>
+      <c r="L34" s="42">
         <v>0</v>
       </c>
       <c r="M34" s="40"/>
@@ -19844,37 +19871,37 @@
       <c r="A35" s="40">
         <v>7</v>
       </c>
-      <c r="B35" s="43">
-        <v>0</v>
-      </c>
-      <c r="C35" s="43">
-        <v>0</v>
-      </c>
-      <c r="D35" s="43">
-        <v>0</v>
-      </c>
-      <c r="E35" s="43">
-        <v>0</v>
-      </c>
-      <c r="F35" s="43">
-        <v>0</v>
-      </c>
-      <c r="G35" s="43">
-        <v>0</v>
-      </c>
-      <c r="H35" s="43">
-        <v>0</v>
-      </c>
-      <c r="I35" s="43">
-        <v>0</v>
-      </c>
-      <c r="J35" s="43">
-        <v>0</v>
-      </c>
-      <c r="K35" s="43">
-        <v>0</v>
-      </c>
-      <c r="L35" s="43">
+      <c r="B35" s="42">
+        <v>0</v>
+      </c>
+      <c r="C35" s="42">
+        <v>0</v>
+      </c>
+      <c r="D35" s="42">
+        <v>0</v>
+      </c>
+      <c r="E35" s="42">
+        <v>0</v>
+      </c>
+      <c r="F35" s="42">
+        <v>0</v>
+      </c>
+      <c r="G35" s="42">
+        <v>0</v>
+      </c>
+      <c r="H35" s="42">
+        <v>0</v>
+      </c>
+      <c r="I35" s="42">
+        <v>0</v>
+      </c>
+      <c r="J35" s="42">
+        <v>0</v>
+      </c>
+      <c r="K35" s="42">
+        <v>0</v>
+      </c>
+      <c r="L35" s="42">
         <v>0</v>
       </c>
       <c r="M35" s="40"/>
@@ -19889,37 +19916,37 @@
       <c r="A36" s="40">
         <v>8</v>
       </c>
-      <c r="B36" s="43">
-        <v>0</v>
-      </c>
-      <c r="C36" s="43">
-        <v>0</v>
-      </c>
-      <c r="D36" s="43">
-        <v>0</v>
-      </c>
-      <c r="E36" s="43">
-        <v>0</v>
-      </c>
-      <c r="F36" s="43">
-        <v>0</v>
-      </c>
-      <c r="G36" s="43">
-        <v>0</v>
-      </c>
-      <c r="H36" s="43">
-        <v>0</v>
-      </c>
-      <c r="I36" s="43">
-        <v>0</v>
-      </c>
-      <c r="J36" s="43">
-        <v>0</v>
-      </c>
-      <c r="K36" s="43">
-        <v>0</v>
-      </c>
-      <c r="L36" s="43">
+      <c r="B36" s="42">
+        <v>0</v>
+      </c>
+      <c r="C36" s="42">
+        <v>0</v>
+      </c>
+      <c r="D36" s="42">
+        <v>0</v>
+      </c>
+      <c r="E36" s="42">
+        <v>0</v>
+      </c>
+      <c r="F36" s="42">
+        <v>0</v>
+      </c>
+      <c r="G36" s="42">
+        <v>0</v>
+      </c>
+      <c r="H36" s="42">
+        <v>0</v>
+      </c>
+      <c r="I36" s="42">
+        <v>0</v>
+      </c>
+      <c r="J36" s="42">
+        <v>0</v>
+      </c>
+      <c r="K36" s="42">
+        <v>0</v>
+      </c>
+      <c r="L36" s="42">
         <v>0</v>
       </c>
       <c r="M36" s="40"/>
@@ -19934,37 +19961,37 @@
       <c r="A37" s="40">
         <v>9</v>
       </c>
-      <c r="B37" s="43">
-        <v>0</v>
-      </c>
-      <c r="C37" s="43">
-        <v>0</v>
-      </c>
-      <c r="D37" s="43">
-        <v>0</v>
-      </c>
-      <c r="E37" s="43">
-        <v>0</v>
-      </c>
-      <c r="F37" s="43">
-        <v>0</v>
-      </c>
-      <c r="G37" s="43">
-        <v>0</v>
-      </c>
-      <c r="H37" s="43">
-        <v>0</v>
-      </c>
-      <c r="I37" s="43">
-        <v>0</v>
-      </c>
-      <c r="J37" s="43">
-        <v>0</v>
-      </c>
-      <c r="K37" s="43">
-        <v>0</v>
-      </c>
-      <c r="L37" s="43">
+      <c r="B37" s="42">
+        <v>0</v>
+      </c>
+      <c r="C37" s="42">
+        <v>0</v>
+      </c>
+      <c r="D37" s="42">
+        <v>0</v>
+      </c>
+      <c r="E37" s="42">
+        <v>0</v>
+      </c>
+      <c r="F37" s="42">
+        <v>0</v>
+      </c>
+      <c r="G37" s="42">
+        <v>0</v>
+      </c>
+      <c r="H37" s="42">
+        <v>0</v>
+      </c>
+      <c r="I37" s="42">
+        <v>0</v>
+      </c>
+      <c r="J37" s="42">
+        <v>0</v>
+      </c>
+      <c r="K37" s="42">
+        <v>0</v>
+      </c>
+      <c r="L37" s="42">
         <v>0</v>
       </c>
       <c r="M37" s="40"/>
@@ -19979,37 +20006,37 @@
       <c r="A38" s="40">
         <v>10</v>
       </c>
-      <c r="B38" s="43">
-        <v>0</v>
-      </c>
-      <c r="C38" s="43">
-        <v>0</v>
-      </c>
-      <c r="D38" s="43">
-        <v>0</v>
-      </c>
-      <c r="E38" s="43">
-        <v>0</v>
-      </c>
-      <c r="F38" s="43">
-        <v>0</v>
-      </c>
-      <c r="G38" s="43">
-        <v>0</v>
-      </c>
-      <c r="H38" s="43">
-        <v>0</v>
-      </c>
-      <c r="I38" s="43">
-        <v>0</v>
-      </c>
-      <c r="J38" s="43">
-        <v>0</v>
-      </c>
-      <c r="K38" s="43">
-        <v>0</v>
-      </c>
-      <c r="L38" s="43">
+      <c r="B38" s="42">
+        <v>0</v>
+      </c>
+      <c r="C38" s="42">
+        <v>0</v>
+      </c>
+      <c r="D38" s="42">
+        <v>0</v>
+      </c>
+      <c r="E38" s="42">
+        <v>0</v>
+      </c>
+      <c r="F38" s="42">
+        <v>0</v>
+      </c>
+      <c r="G38" s="42">
+        <v>0</v>
+      </c>
+      <c r="H38" s="42">
+        <v>0</v>
+      </c>
+      <c r="I38" s="42">
+        <v>0</v>
+      </c>
+      <c r="J38" s="42">
+        <v>0</v>
+      </c>
+      <c r="K38" s="42">
+        <v>0</v>
+      </c>
+      <c r="L38" s="42">
         <v>0</v>
       </c>
       <c r="M38" s="40"/>
@@ -20024,37 +20051,37 @@
       <c r="A39" s="40">
         <v>11</v>
       </c>
-      <c r="B39" s="43">
-        <v>0</v>
-      </c>
-      <c r="C39" s="43">
-        <v>0</v>
-      </c>
-      <c r="D39" s="43">
-        <v>0</v>
-      </c>
-      <c r="E39" s="43">
-        <v>0</v>
-      </c>
-      <c r="F39" s="43">
-        <v>0</v>
-      </c>
-      <c r="G39" s="43">
-        <v>0</v>
-      </c>
-      <c r="H39" s="43">
-        <v>0</v>
-      </c>
-      <c r="I39" s="43">
-        <v>0</v>
-      </c>
-      <c r="J39" s="43">
-        <v>0</v>
-      </c>
-      <c r="K39" s="43">
-        <v>0</v>
-      </c>
-      <c r="L39" s="43">
+      <c r="B39" s="42">
+        <v>0</v>
+      </c>
+      <c r="C39" s="42">
+        <v>0</v>
+      </c>
+      <c r="D39" s="42">
+        <v>0</v>
+      </c>
+      <c r="E39" s="42">
+        <v>0</v>
+      </c>
+      <c r="F39" s="42">
+        <v>0</v>
+      </c>
+      <c r="G39" s="42">
+        <v>0</v>
+      </c>
+      <c r="H39" s="42">
+        <v>0</v>
+      </c>
+      <c r="I39" s="42">
+        <v>0</v>
+      </c>
+      <c r="J39" s="42">
+        <v>0</v>
+      </c>
+      <c r="K39" s="42">
+        <v>0</v>
+      </c>
+      <c r="L39" s="42">
         <v>0</v>
       </c>
       <c r="M39" s="40"/>
@@ -20069,37 +20096,37 @@
       <c r="A40" s="40">
         <v>12</v>
       </c>
-      <c r="B40" s="43">
-        <v>0</v>
-      </c>
-      <c r="C40" s="43">
-        <v>0</v>
-      </c>
-      <c r="D40" s="43">
-        <v>0</v>
-      </c>
-      <c r="E40" s="43">
-        <v>0</v>
-      </c>
-      <c r="F40" s="43">
-        <v>0</v>
-      </c>
-      <c r="G40" s="43">
-        <v>0</v>
-      </c>
-      <c r="H40" s="43">
-        <v>0</v>
-      </c>
-      <c r="I40" s="43">
-        <v>0</v>
-      </c>
-      <c r="J40" s="43">
-        <v>0</v>
-      </c>
-      <c r="K40" s="43">
+      <c r="B40" s="42">
+        <v>0</v>
+      </c>
+      <c r="C40" s="42">
+        <v>0</v>
+      </c>
+      <c r="D40" s="42">
+        <v>0</v>
+      </c>
+      <c r="E40" s="42">
+        <v>0</v>
+      </c>
+      <c r="F40" s="42">
+        <v>0</v>
+      </c>
+      <c r="G40" s="42">
+        <v>0</v>
+      </c>
+      <c r="H40" s="42">
+        <v>0</v>
+      </c>
+      <c r="I40" s="42">
+        <v>0</v>
+      </c>
+      <c r="J40" s="42">
+        <v>0</v>
+      </c>
+      <c r="K40" s="42">
         <v>4.9999999999994398E-5</v>
       </c>
-      <c r="L40" s="43">
+      <c r="L40" s="42">
         <v>4.9999999999994398E-5</v>
       </c>
       <c r="M40" s="40"/>
@@ -20114,37 +20141,37 @@
       <c r="A41" s="40">
         <v>13</v>
       </c>
-      <c r="B41" s="43">
-        <v>0</v>
-      </c>
-      <c r="C41" s="43">
-        <v>0</v>
-      </c>
-      <c r="D41" s="43">
-        <v>0</v>
-      </c>
-      <c r="E41" s="43">
-        <v>0</v>
-      </c>
-      <c r="F41" s="43">
-        <v>0</v>
-      </c>
-      <c r="G41" s="43">
-        <v>0</v>
-      </c>
-      <c r="H41" s="43">
-        <v>0</v>
-      </c>
-      <c r="I41" s="43">
-        <v>0</v>
-      </c>
-      <c r="J41" s="43">
+      <c r="B41" s="42">
+        <v>0</v>
+      </c>
+      <c r="C41" s="42">
+        <v>0</v>
+      </c>
+      <c r="D41" s="42">
+        <v>0</v>
+      </c>
+      <c r="E41" s="42">
+        <v>0</v>
+      </c>
+      <c r="F41" s="42">
+        <v>0</v>
+      </c>
+      <c r="G41" s="42">
+        <v>0</v>
+      </c>
+      <c r="H41" s="42">
+        <v>0</v>
+      </c>
+      <c r="I41" s="42">
+        <v>0</v>
+      </c>
+      <c r="J41" s="42">
         <v>4.9999999999994398E-5</v>
       </c>
-      <c r="K41" s="43">
+      <c r="K41" s="42">
         <v>4.9999999999994398E-5</v>
       </c>
-      <c r="L41" s="43">
+      <c r="L41" s="42">
         <v>4.9999999999994396E-4</v>
       </c>
       <c r="M41" s="40"/>
@@ -20159,37 +20186,37 @@
       <c r="A42" s="40">
         <v>14</v>
       </c>
-      <c r="B42" s="43">
-        <v>0</v>
-      </c>
-      <c r="C42" s="43">
-        <v>0</v>
-      </c>
-      <c r="D42" s="43">
-        <v>0</v>
-      </c>
-      <c r="E42" s="43">
-        <v>0</v>
-      </c>
-      <c r="F42" s="43">
-        <v>0</v>
-      </c>
-      <c r="G42" s="43">
-        <v>0</v>
-      </c>
-      <c r="H42" s="43">
-        <v>0</v>
-      </c>
-      <c r="I42" s="43">
+      <c r="B42" s="42">
+        <v>0</v>
+      </c>
+      <c r="C42" s="42">
+        <v>0</v>
+      </c>
+      <c r="D42" s="42">
+        <v>0</v>
+      </c>
+      <c r="E42" s="42">
+        <v>0</v>
+      </c>
+      <c r="F42" s="42">
+        <v>0</v>
+      </c>
+      <c r="G42" s="42">
+        <v>0</v>
+      </c>
+      <c r="H42" s="42">
+        <v>0</v>
+      </c>
+      <c r="I42" s="42">
         <v>4.9999999999994398E-5</v>
       </c>
-      <c r="J42" s="43">
+      <c r="J42" s="42">
         <v>4.9999999999994398E-5</v>
       </c>
-      <c r="K42" s="43">
+      <c r="K42" s="42">
         <v>3.4999999999996102E-4</v>
       </c>
-      <c r="L42" s="43">
+      <c r="L42" s="42">
         <v>2.1499999999999801E-3</v>
       </c>
       <c r="M42" s="40"/>
@@ -20204,37 +20231,37 @@
       <c r="A43" s="40">
         <v>15</v>
       </c>
-      <c r="B43" s="43">
-        <v>0</v>
-      </c>
-      <c r="C43" s="43">
-        <v>0</v>
-      </c>
-      <c r="D43" s="43">
-        <v>0</v>
-      </c>
-      <c r="E43" s="43">
-        <v>0</v>
-      </c>
-      <c r="F43" s="43">
-        <v>0</v>
-      </c>
-      <c r="G43" s="43">
-        <v>0</v>
-      </c>
-      <c r="H43" s="43">
-        <v>0</v>
-      </c>
-      <c r="I43" s="43">
+      <c r="B43" s="42">
+        <v>0</v>
+      </c>
+      <c r="C43" s="42">
+        <v>0</v>
+      </c>
+      <c r="D43" s="42">
+        <v>0</v>
+      </c>
+      <c r="E43" s="42">
+        <v>0</v>
+      </c>
+      <c r="F43" s="42">
+        <v>0</v>
+      </c>
+      <c r="G43" s="42">
+        <v>0</v>
+      </c>
+      <c r="H43" s="42">
+        <v>0</v>
+      </c>
+      <c r="I43" s="42">
         <v>4.9999999999994398E-5</v>
       </c>
-      <c r="J43" s="43">
+      <c r="J43" s="42">
         <v>2.4999999999997198E-4</v>
       </c>
-      <c r="K43" s="43">
+      <c r="K43" s="42">
         <v>1.75000000000002E-3</v>
       </c>
-      <c r="L43" s="43">
+      <c r="L43" s="42">
         <v>5.0499999999999903E-3</v>
       </c>
       <c r="M43" s="40"/>
@@ -20249,37 +20276,37 @@
       <c r="A44" s="40">
         <v>16</v>
       </c>
-      <c r="B44" s="43">
-        <v>0</v>
-      </c>
-      <c r="C44" s="43">
-        <v>0</v>
-      </c>
-      <c r="D44" s="43">
-        <v>0</v>
-      </c>
-      <c r="E44" s="43">
-        <v>0</v>
-      </c>
-      <c r="F44" s="43">
-        <v>0</v>
-      </c>
-      <c r="G44" s="43">
-        <v>0</v>
-      </c>
-      <c r="H44" s="43">
+      <c r="B44" s="42">
+        <v>0</v>
+      </c>
+      <c r="C44" s="42">
+        <v>0</v>
+      </c>
+      <c r="D44" s="42">
+        <v>0</v>
+      </c>
+      <c r="E44" s="42">
+        <v>0</v>
+      </c>
+      <c r="F44" s="42">
+        <v>0</v>
+      </c>
+      <c r="G44" s="42">
+        <v>0</v>
+      </c>
+      <c r="H44" s="42">
         <v>4.9999999999994398E-5</v>
       </c>
-      <c r="I44" s="43">
+      <c r="I44" s="42">
         <v>9.9999999999988905E-5</v>
       </c>
-      <c r="J44" s="43">
+      <c r="J44" s="42">
         <v>1.04999999999999E-3</v>
       </c>
-      <c r="K44" s="43">
+      <c r="K44" s="42">
         <v>3.7000000000000301E-3</v>
       </c>
-      <c r="L44" s="43">
+      <c r="L44" s="42">
         <v>1.1849999999999999E-2</v>
       </c>
       <c r="M44" s="40"/>
@@ -20294,37 +20321,37 @@
       <c r="A45" s="40">
         <v>17</v>
       </c>
-      <c r="B45" s="43">
-        <v>0</v>
-      </c>
-      <c r="C45" s="43">
-        <v>0</v>
-      </c>
-      <c r="D45" s="43">
-        <v>0</v>
-      </c>
-      <c r="E45" s="43">
-        <v>0</v>
-      </c>
-      <c r="F45" s="43">
-        <v>0</v>
-      </c>
-      <c r="G45" s="43">
+      <c r="B45" s="42">
+        <v>0</v>
+      </c>
+      <c r="C45" s="42">
+        <v>0</v>
+      </c>
+      <c r="D45" s="42">
+        <v>0</v>
+      </c>
+      <c r="E45" s="42">
+        <v>0</v>
+      </c>
+      <c r="F45" s="42">
+        <v>0</v>
+      </c>
+      <c r="G45" s="42">
         <v>4.9999999999994398E-5</v>
       </c>
-      <c r="H45" s="43">
+      <c r="H45" s="42">
         <v>4.9999999999994398E-5</v>
       </c>
-      <c r="I45" s="43">
+      <c r="I45" s="42">
         <v>4.4999999999995001E-4</v>
       </c>
-      <c r="J45" s="43">
+      <c r="J45" s="42">
         <v>2.5500000000000501E-3</v>
       </c>
-      <c r="K45" s="43">
+      <c r="K45" s="42">
         <v>8.0499999999999999E-3</v>
       </c>
-      <c r="L45" s="43">
+      <c r="L45" s="42">
         <v>2.1000000000000001E-2</v>
       </c>
       <c r="M45" s="40"/>
@@ -20339,37 +20366,37 @@
       <c r="A46" s="40">
         <v>18</v>
       </c>
-      <c r="B46" s="43">
-        <v>0</v>
-      </c>
-      <c r="C46" s="43">
-        <v>0</v>
-      </c>
-      <c r="D46" s="43">
-        <v>0</v>
-      </c>
-      <c r="E46" s="43">
-        <v>0</v>
-      </c>
-      <c r="F46" s="43">
-        <v>0</v>
-      </c>
-      <c r="G46" s="43">
+      <c r="B46" s="42">
+        <v>0</v>
+      </c>
+      <c r="C46" s="42">
+        <v>0</v>
+      </c>
+      <c r="D46" s="42">
+        <v>0</v>
+      </c>
+      <c r="E46" s="42">
+        <v>0</v>
+      </c>
+      <c r="F46" s="42">
+        <v>0</v>
+      </c>
+      <c r="G46" s="42">
         <v>4.9999999999994398E-5</v>
       </c>
-      <c r="H46" s="43">
+      <c r="H46" s="42">
         <v>9.9999999999988905E-5</v>
       </c>
-      <c r="I46" s="43">
+      <c r="I46" s="42">
         <v>1.19999999999997E-3</v>
       </c>
-      <c r="J46" s="43">
+      <c r="J46" s="42">
         <v>5.0499999999999903E-3</v>
       </c>
-      <c r="K46" s="43">
+      <c r="K46" s="42">
         <v>1.5249999999999901E-2</v>
       </c>
-      <c r="L46" s="43">
+      <c r="L46" s="42">
         <v>3.4599999999999902E-2</v>
       </c>
       <c r="M46" s="40"/>
@@ -20384,37 +20411,37 @@
       <c r="A47" s="40">
         <v>19</v>
       </c>
-      <c r="B47" s="43">
-        <v>0</v>
-      </c>
-      <c r="C47" s="43">
-        <v>0</v>
-      </c>
-      <c r="D47" s="43">
-        <v>0</v>
-      </c>
-      <c r="E47" s="43">
-        <v>0</v>
-      </c>
-      <c r="F47" s="43">
+      <c r="B47" s="42">
+        <v>0</v>
+      </c>
+      <c r="C47" s="42">
+        <v>0</v>
+      </c>
+      <c r="D47" s="42">
+        <v>0</v>
+      </c>
+      <c r="E47" s="42">
+        <v>0</v>
+      </c>
+      <c r="F47" s="42">
         <v>4.9999999999994398E-5</v>
       </c>
-      <c r="G47" s="43">
+      <c r="G47" s="42">
         <v>4.9999999999994398E-5</v>
       </c>
-      <c r="H47" s="43">
+      <c r="H47" s="42">
         <v>4.9999999999994396E-4</v>
       </c>
-      <c r="I47" s="43">
+      <c r="I47" s="42">
         <v>2.8500000000000101E-3</v>
       </c>
-      <c r="J47" s="43">
+      <c r="J47" s="42">
         <v>8.95000000000001E-3</v>
       </c>
-      <c r="K47" s="43">
+      <c r="K47" s="42">
         <v>2.385E-2</v>
       </c>
-      <c r="L47" s="43">
+      <c r="L47" s="42">
         <v>5.3350000000000002E-2</v>
       </c>
       <c r="M47" s="40"/>
@@ -20429,37 +20456,37 @@
       <c r="A48" s="40">
         <v>20</v>
       </c>
-      <c r="B48" s="43">
-        <v>0</v>
-      </c>
-      <c r="C48" s="43">
-        <v>0</v>
-      </c>
-      <c r="D48" s="43">
-        <v>0</v>
-      </c>
-      <c r="E48" s="43">
-        <v>0</v>
-      </c>
-      <c r="F48" s="43">
+      <c r="B48" s="42">
+        <v>0</v>
+      </c>
+      <c r="C48" s="42">
+        <v>0</v>
+      </c>
+      <c r="D48" s="42">
+        <v>0</v>
+      </c>
+      <c r="E48" s="42">
+        <v>0</v>
+      </c>
+      <c r="F48" s="42">
         <v>4.9999999999994398E-5</v>
       </c>
-      <c r="G48" s="43">
+      <c r="G48" s="42">
         <v>9.9999999999988905E-5</v>
       </c>
-      <c r="H48" s="43">
+      <c r="H48" s="42">
         <v>9.5000000000000596E-4</v>
       </c>
-      <c r="I48" s="43">
+      <c r="I48" s="42">
         <v>4.9500000000000099E-3</v>
       </c>
-      <c r="J48" s="43">
+      <c r="J48" s="42">
         <v>1.495E-2</v>
       </c>
-      <c r="K48" s="43">
+      <c r="K48" s="42">
         <v>3.5449999999999898E-2</v>
       </c>
-      <c r="L48" s="43">
+      <c r="L48" s="42">
         <v>7.4799999999999894E-2</v>
       </c>
       <c r="M48" s="40"/>
@@ -20472,17 +20499,17 @@
     </row>
     <row r="49" spans="1:19">
       <c r="A49" s="40"/>
-      <c r="B49" s="45"/>
-      <c r="C49" s="45"/>
-      <c r="D49" s="45"/>
-      <c r="E49" s="45"/>
-      <c r="F49" s="45"/>
-      <c r="G49" s="45"/>
-      <c r="H49" s="45"/>
-      <c r="I49" s="45"/>
-      <c r="J49" s="45"/>
-      <c r="K49" s="45"/>
-      <c r="L49" s="45"/>
+      <c r="B49" s="44"/>
+      <c r="C49" s="44"/>
+      <c r="D49" s="44"/>
+      <c r="E49" s="44"/>
+      <c r="F49" s="44"/>
+      <c r="G49" s="44"/>
+      <c r="H49" s="44"/>
+      <c r="I49" s="44"/>
+      <c r="J49" s="44"/>
+      <c r="K49" s="44"/>
+      <c r="L49" s="44"/>
       <c r="M49" s="40"/>
       <c r="N49" s="40"/>
       <c r="O49" s="40"/>
@@ -20493,17 +20520,17 @@
     </row>
     <row r="50" spans="1:19">
       <c r="A50" s="40"/>
-      <c r="B50" s="45"/>
-      <c r="C50" s="45"/>
-      <c r="D50" s="45"/>
-      <c r="E50" s="45"/>
-      <c r="F50" s="45"/>
-      <c r="G50" s="45"/>
-      <c r="H50" s="45"/>
-      <c r="I50" s="45"/>
-      <c r="J50" s="45"/>
-      <c r="K50" s="45"/>
-      <c r="L50" s="45"/>
+      <c r="B50" s="44"/>
+      <c r="C50" s="44"/>
+      <c r="D50" s="44"/>
+      <c r="E50" s="44"/>
+      <c r="F50" s="44"/>
+      <c r="G50" s="44"/>
+      <c r="H50" s="44"/>
+      <c r="I50" s="44"/>
+      <c r="J50" s="44"/>
+      <c r="K50" s="44"/>
+      <c r="L50" s="44"/>
       <c r="M50" s="40"/>
       <c r="N50" s="40"/>
       <c r="O50" s="40"/>
@@ -20514,17 +20541,17 @@
     </row>
     <row r="51" spans="1:19">
       <c r="A51" s="40"/>
-      <c r="B51" s="45"/>
-      <c r="C51" s="45"/>
-      <c r="D51" s="45"/>
-      <c r="E51" s="45"/>
-      <c r="F51" s="45"/>
-      <c r="G51" s="45"/>
-      <c r="H51" s="45"/>
-      <c r="I51" s="45"/>
-      <c r="J51" s="45"/>
-      <c r="K51" s="45"/>
-      <c r="L51" s="45"/>
+      <c r="B51" s="44"/>
+      <c r="C51" s="44"/>
+      <c r="D51" s="44"/>
+      <c r="E51" s="44"/>
+      <c r="F51" s="44"/>
+      <c r="G51" s="44"/>
+      <c r="H51" s="44"/>
+      <c r="I51" s="44"/>
+      <c r="J51" s="44"/>
+      <c r="K51" s="44"/>
+      <c r="L51" s="44"/>
       <c r="M51" s="40"/>
       <c r="N51" s="40"/>
       <c r="O51" s="40"/>
@@ -20535,17 +20562,17 @@
     </row>
     <row r="52" spans="1:19">
       <c r="A52" s="40"/>
-      <c r="B52" s="45"/>
-      <c r="C52" s="45"/>
-      <c r="D52" s="45"/>
-      <c r="E52" s="45"/>
-      <c r="F52" s="45"/>
-      <c r="G52" s="45"/>
-      <c r="H52" s="45"/>
-      <c r="I52" s="45"/>
-      <c r="J52" s="45"/>
-      <c r="K52" s="45"/>
-      <c r="L52" s="45"/>
+      <c r="B52" s="44"/>
+      <c r="C52" s="44"/>
+      <c r="D52" s="44"/>
+      <c r="E52" s="44"/>
+      <c r="F52" s="44"/>
+      <c r="G52" s="44"/>
+      <c r="H52" s="44"/>
+      <c r="I52" s="44"/>
+      <c r="J52" s="44"/>
+      <c r="K52" s="44"/>
+      <c r="L52" s="44"/>
       <c r="M52" s="40"/>
       <c r="N52" s="40"/>
       <c r="O52" s="40"/>
@@ -20556,17 +20583,17 @@
     </row>
     <row r="53" spans="1:19">
       <c r="A53" s="40"/>
-      <c r="B53" s="45"/>
-      <c r="C53" s="45"/>
-      <c r="D53" s="45"/>
-      <c r="E53" s="45"/>
-      <c r="F53" s="45"/>
-      <c r="G53" s="45"/>
-      <c r="H53" s="45"/>
-      <c r="I53" s="45"/>
-      <c r="J53" s="45"/>
-      <c r="K53" s="45"/>
-      <c r="L53" s="45"/>
+      <c r="B53" s="44"/>
+      <c r="C53" s="44"/>
+      <c r="D53" s="44"/>
+      <c r="E53" s="44"/>
+      <c r="F53" s="44"/>
+      <c r="G53" s="44"/>
+      <c r="H53" s="44"/>
+      <c r="I53" s="44"/>
+      <c r="J53" s="44"/>
+      <c r="K53" s="44"/>
+      <c r="L53" s="44"/>
       <c r="M53" s="40"/>
       <c r="N53" s="40"/>
       <c r="O53" s="40"/>
@@ -20577,17 +20604,17 @@
     </row>
     <row r="54" spans="1:19">
       <c r="A54" s="40"/>
-      <c r="B54" s="45"/>
-      <c r="C54" s="45"/>
-      <c r="D54" s="45"/>
-      <c r="E54" s="45"/>
-      <c r="F54" s="45"/>
-      <c r="G54" s="45"/>
-      <c r="H54" s="45"/>
-      <c r="I54" s="45"/>
-      <c r="J54" s="45"/>
-      <c r="K54" s="45"/>
-      <c r="L54" s="45"/>
+      <c r="B54" s="44"/>
+      <c r="C54" s="44"/>
+      <c r="D54" s="44"/>
+      <c r="E54" s="44"/>
+      <c r="F54" s="44"/>
+      <c r="G54" s="44"/>
+      <c r="H54" s="44"/>
+      <c r="I54" s="44"/>
+      <c r="J54" s="44"/>
+      <c r="K54" s="44"/>
+      <c r="L54" s="44"/>
       <c r="M54" s="40"/>
       <c r="N54" s="40"/>
       <c r="O54" s="40"/>
@@ -20598,17 +20625,17 @@
     </row>
     <row r="55" spans="1:19">
       <c r="A55" s="40"/>
-      <c r="B55" s="45"/>
-      <c r="C55" s="45"/>
-      <c r="D55" s="45"/>
-      <c r="E55" s="45"/>
-      <c r="F55" s="45"/>
-      <c r="G55" s="45"/>
-      <c r="H55" s="45"/>
-      <c r="I55" s="45"/>
-      <c r="J55" s="45"/>
-      <c r="K55" s="45"/>
-      <c r="L55" s="45"/>
+      <c r="B55" s="44"/>
+      <c r="C55" s="44"/>
+      <c r="D55" s="44"/>
+      <c r="E55" s="44"/>
+      <c r="F55" s="44"/>
+      <c r="G55" s="44"/>
+      <c r="H55" s="44"/>
+      <c r="I55" s="44"/>
+      <c r="J55" s="44"/>
+      <c r="K55" s="44"/>
+      <c r="L55" s="44"/>
       <c r="M55" s="40"/>
       <c r="N55" s="40"/>
       <c r="O55" s="40"/>
@@ -20625,15 +20652,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B11B375A-1BBD-3942-A9A9-E5A4DDCCCBA0}">
-  <dimension ref="A1:N56"/>
+  <dimension ref="A1:N62"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="24.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.1640625" style="43" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" s="40"/>
-      <c r="B1" s="40">
+      <c r="B1" s="44">
         <v>0</v>
       </c>
       <c r="C1" s="40"/>
@@ -20653,7 +20681,7 @@
       <c r="A2" s="40" t="s">
         <v>84</v>
       </c>
-      <c r="B2" s="42">
+      <c r="B2" s="41">
         <v>8.6024742893045791E-3</v>
       </c>
       <c r="C2" s="40"/>
@@ -20673,7 +20701,7 @@
       <c r="A3" s="40" t="s">
         <v>87</v>
       </c>
-      <c r="B3" s="42">
+      <c r="B3" s="41">
         <v>3.2801500345226997E-2</v>
       </c>
       <c r="C3" s="40"/>
@@ -20693,7 +20721,7 @@
       <c r="A4" s="40" t="s">
         <v>109</v>
       </c>
-      <c r="B4" s="42">
+      <c r="B4" s="41">
         <f>SUM(B5:B7)</f>
         <v>0.4582721463401897</v>
       </c>
@@ -20714,7 +20742,7 @@
       <c r="A5" s="40" t="s">
         <v>90</v>
       </c>
-      <c r="B5" s="42">
+      <c r="B5" s="41">
         <v>0.19740877689904199</v>
       </c>
       <c r="C5" s="40"/>
@@ -20734,7 +20762,7 @@
       <c r="A6" s="40" t="s">
         <v>91</v>
       </c>
-      <c r="B6" s="42">
+      <c r="B6" s="41">
         <v>0.18908471834031801</v>
       </c>
       <c r="C6" s="40"/>
@@ -20754,7 +20782,7 @@
       <c r="A7" s="40" t="s">
         <v>92</v>
       </c>
-      <c r="B7" s="42">
+      <c r="B7" s="41">
         <v>7.1778651100829705E-2</v>
       </c>
       <c r="C7" s="40"/>
@@ -20774,7 +20802,7 @@
       <c r="A8" s="40" t="s">
         <v>93</v>
       </c>
-      <c r="B8" s="42">
+      <c r="B8" s="41">
         <v>7.3157780722153398E-2</v>
       </c>
       <c r="C8" s="40"/>
@@ -20794,7 +20822,7 @@
       <c r="A9" s="40" t="s">
         <v>94</v>
       </c>
-      <c r="B9" s="42">
+      <c r="B9" s="41">
         <v>1.87236840825202E-2</v>
       </c>
       <c r="C9" s="40"/>
@@ -20814,7 +20842,7 @@
       <c r="A10" s="40" t="s">
         <v>95</v>
       </c>
-      <c r="B10" s="42">
+      <c r="B10" s="41">
         <v>2.97933991652987E-2</v>
       </c>
       <c r="C10" s="40"/>
@@ -20834,7 +20862,7 @@
       <c r="A11" s="40" t="s">
         <v>96</v>
       </c>
-      <c r="B11" s="42">
+      <c r="B11" s="41">
         <v>1.54976214370223E-2</v>
       </c>
       <c r="C11" s="40"/>
@@ -20854,7 +20882,7 @@
       <c r="A12" s="40" t="s">
         <v>97</v>
       </c>
-      <c r="B12" s="42">
+      <c r="B12" s="41">
         <v>1.97275781635846E-2</v>
       </c>
       <c r="C12" s="40"/>
@@ -20874,7 +20902,7 @@
       <c r="A13" s="40" t="s">
         <v>98</v>
       </c>
-      <c r="B13" s="42">
+      <c r="B13" s="41">
         <v>1.01151456589024E-2</v>
       </c>
       <c r="C13" s="40"/>
@@ -20894,7 +20922,7 @@
       <c r="A14" s="40" t="s">
         <v>99</v>
       </c>
-      <c r="B14" s="42">
+      <c r="B14" s="41">
         <v>1.17981976649371E-2</v>
       </c>
       <c r="C14" s="40"/>
@@ -20914,7 +20942,7 @@
       <c r="A15" s="40" t="s">
         <v>100</v>
       </c>
-      <c r="B15" s="42">
+      <c r="B15" s="41">
         <v>5.1275847854916597E-3</v>
       </c>
       <c r="C15" s="40"/>
@@ -20934,7 +20962,7 @@
       <c r="A16" s="40" t="s">
         <v>101</v>
       </c>
-      <c r="B16" s="42">
+      <c r="B16" s="41">
         <v>1.5793800933559501E-2</v>
       </c>
       <c r="C16" s="40"/>
@@ -20954,7 +20982,7 @@
       <c r="A17" s="40" t="s">
         <v>102</v>
       </c>
-      <c r="B17" s="42">
+      <c r="B17" s="41">
         <v>3.4977493858902998E-3</v>
       </c>
       <c r="C17" s="40"/>
@@ -20974,7 +21002,7 @@
       <c r="A18" s="40" t="s">
         <v>103</v>
       </c>
-      <c r="B18" s="42">
+      <c r="B18" s="41">
         <v>0.15256482789336701</v>
       </c>
       <c r="C18" s="40"/>
@@ -20994,7 +21022,7 @@
       <c r="A19" s="40" t="s">
         <v>104</v>
       </c>
-      <c r="B19" s="42">
+      <c r="B19" s="41">
         <v>5.3093620137906E-2</v>
       </c>
       <c r="C19" s="40"/>
@@ -21014,7 +21042,7 @@
       <c r="A20" s="40" t="s">
         <v>105</v>
       </c>
-      <c r="B20" s="42">
+      <c r="B20" s="41">
         <v>1.5460685206523699E-2</v>
       </c>
       <c r="C20" s="40"/>
@@ -21034,7 +21062,7 @@
       <c r="A21" s="40" t="s">
         <v>106</v>
       </c>
-      <c r="B21" s="42">
+      <c r="B21" s="41">
         <v>3.23569923114434E-2</v>
       </c>
       <c r="C21" s="40"/>
@@ -21054,7 +21082,7 @@
       <c r="A22" s="40" t="s">
         <v>107</v>
       </c>
-      <c r="B22" s="42">
+      <c r="B22" s="41">
         <v>2.0805473063830501E-2</v>
       </c>
       <c r="C22" s="40"/>
@@ -21074,7 +21102,7 @@
       <c r="A23" s="40" t="s">
         <v>108</v>
       </c>
-      <c r="B23" s="42">
+      <c r="B23" s="41">
         <v>2.28097384128455E-2</v>
       </c>
       <c r="C23" s="40"/>
@@ -21092,7 +21120,7 @@
     </row>
     <row r="24" spans="1:14">
       <c r="A24" s="40"/>
-      <c r="B24" s="40"/>
+      <c r="B24" s="44"/>
       <c r="C24" s="40"/>
       <c r="D24" s="40"/>
       <c r="E24" s="40"/>
@@ -21108,7 +21136,7 @@
     </row>
     <row r="25" spans="1:14">
       <c r="A25" s="40"/>
-      <c r="B25" s="40"/>
+      <c r="B25" s="44"/>
       <c r="C25" s="40"/>
       <c r="D25" s="40"/>
       <c r="E25" s="40"/>
@@ -21124,7 +21152,7 @@
     </row>
     <row r="26" spans="1:14">
       <c r="A26" s="40"/>
-      <c r="B26" s="40"/>
+      <c r="B26" s="44"/>
       <c r="C26" s="40"/>
       <c r="D26" s="40"/>
       <c r="E26" s="40"/>
@@ -21140,7 +21168,7 @@
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="40"/>
-      <c r="B27" s="40"/>
+      <c r="B27" s="44"/>
       <c r="C27" s="40"/>
       <c r="D27" s="40"/>
       <c r="E27" s="40"/>
@@ -21154,209 +21182,396 @@
       <c r="M27" s="40"/>
       <c r="N27" s="40"/>
     </row>
+    <row r="29" spans="1:14">
+      <c r="C29" s="40"/>
+      <c r="D29" s="40"/>
+      <c r="E29" s="40"/>
+      <c r="F29" s="40"/>
+      <c r="G29" s="40"/>
+      <c r="H29" s="40"/>
+      <c r="I29" s="40"/>
+    </row>
+    <row r="30" spans="1:14">
+      <c r="C30" s="40"/>
+      <c r="D30" s="40"/>
+      <c r="E30" s="40"/>
+      <c r="F30" s="40"/>
+      <c r="G30" s="40"/>
+      <c r="H30" s="40"/>
+      <c r="I30" s="40"/>
+    </row>
     <row r="31" spans="1:14">
-      <c r="B31">
-        <v>0</v>
-      </c>
+      <c r="B31" s="43">
+        <v>0</v>
+      </c>
+      <c r="C31" s="40"/>
+      <c r="D31" s="40"/>
+      <c r="E31" s="40"/>
+      <c r="F31" s="40"/>
+      <c r="G31" s="40"/>
+      <c r="H31" s="40"/>
+      <c r="I31" s="40"/>
     </row>
     <row r="32" spans="1:14">
       <c r="A32" t="s">
         <v>84</v>
       </c>
-      <c r="B32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2">
+      <c r="B32" s="43">
+        <v>0</v>
+      </c>
+      <c r="C32" s="40"/>
+      <c r="D32" s="40"/>
+      <c r="E32" s="40"/>
+      <c r="F32" s="40"/>
+      <c r="G32" s="40"/>
+      <c r="H32" s="40"/>
+      <c r="I32" s="40"/>
+    </row>
+    <row r="33" spans="1:9">
       <c r="A33" t="s">
         <v>85</v>
       </c>
-      <c r="B33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2">
+      <c r="B33" s="43">
+        <v>0</v>
+      </c>
+      <c r="C33" s="40"/>
+      <c r="D33" s="40"/>
+      <c r="E33" s="40"/>
+      <c r="F33" s="40"/>
+      <c r="G33" s="40"/>
+      <c r="H33" s="40"/>
+      <c r="I33" s="40"/>
+    </row>
+    <row r="34" spans="1:9">
       <c r="A34" t="s">
         <v>86</v>
       </c>
-      <c r="B34">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2">
+      <c r="B34" s="43">
+        <v>0</v>
+      </c>
+      <c r="C34" s="40"/>
+      <c r="D34" s="40"/>
+      <c r="E34" s="40"/>
+      <c r="F34" s="40"/>
+      <c r="G34" s="40"/>
+      <c r="H34" s="40"/>
+      <c r="I34" s="40"/>
+    </row>
+    <row r="35" spans="1:9">
       <c r="A35" t="s">
         <v>87</v>
       </c>
-      <c r="B35">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2">
+      <c r="B35" s="43">
+        <v>0</v>
+      </c>
+      <c r="C35" s="40"/>
+      <c r="D35" s="40"/>
+      <c r="E35" s="40"/>
+      <c r="F35" s="40"/>
+      <c r="G35" s="40"/>
+      <c r="H35" s="40"/>
+      <c r="I35" s="40"/>
+    </row>
+    <row r="36" spans="1:9">
       <c r="A36" t="s">
         <v>88</v>
       </c>
-      <c r="B36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2">
+      <c r="B36" s="43">
+        <v>0</v>
+      </c>
+      <c r="C36" s="40"/>
+      <c r="D36" s="40"/>
+      <c r="E36" s="40"/>
+      <c r="F36" s="40"/>
+      <c r="G36" s="40"/>
+      <c r="H36" s="40"/>
+      <c r="I36" s="40"/>
+    </row>
+    <row r="37" spans="1:9">
       <c r="A37" t="s">
         <v>89</v>
       </c>
-      <c r="B37">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2">
+      <c r="B37" s="43">
+        <v>0</v>
+      </c>
+      <c r="C37" s="40"/>
+      <c r="D37" s="40"/>
+      <c r="E37" s="40"/>
+      <c r="F37" s="40"/>
+      <c r="G37" s="40"/>
+      <c r="H37" s="40"/>
+      <c r="I37" s="40"/>
+    </row>
+    <row r="38" spans="1:9">
       <c r="A38" t="s">
         <v>90</v>
       </c>
-      <c r="B38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2">
+      <c r="B38" s="43">
+        <v>0</v>
+      </c>
+      <c r="C38" s="40"/>
+      <c r="D38" s="40"/>
+      <c r="E38" s="40"/>
+      <c r="F38" s="40"/>
+      <c r="G38" s="40"/>
+      <c r="H38" s="40"/>
+      <c r="I38" s="40"/>
+    </row>
+    <row r="39" spans="1:9">
       <c r="A39" t="s">
         <v>91</v>
       </c>
-      <c r="B39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2">
+      <c r="B39" s="43">
+        <v>0</v>
+      </c>
+      <c r="C39" s="40"/>
+      <c r="D39" s="40"/>
+      <c r="E39" s="40"/>
+      <c r="F39" s="40"/>
+      <c r="G39" s="40"/>
+      <c r="H39" s="40"/>
+      <c r="I39" s="40"/>
+    </row>
+    <row r="40" spans="1:9">
       <c r="A40" t="s">
         <v>92</v>
       </c>
-      <c r="B40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2">
+      <c r="B40" s="43">
+        <v>0</v>
+      </c>
+      <c r="C40" s="40"/>
+      <c r="D40" s="40"/>
+      <c r="E40" s="40"/>
+      <c r="F40" s="40"/>
+      <c r="G40" s="40"/>
+      <c r="H40" s="40"/>
+      <c r="I40" s="40"/>
+    </row>
+    <row r="41" spans="1:9">
       <c r="A41" t="s">
         <v>110</v>
       </c>
-      <c r="B41" s="41">
+      <c r="B41" s="88">
         <v>1.9086594707416901E-2</v>
       </c>
-    </row>
-    <row r="42" spans="1:2">
+      <c r="C41" s="40"/>
+      <c r="D41" s="40"/>
+      <c r="E41" s="40"/>
+      <c r="F41" s="40"/>
+      <c r="G41" s="40"/>
+      <c r="H41" s="40"/>
+      <c r="I41" s="40"/>
+    </row>
+    <row r="42" spans="1:9">
       <c r="A42" t="s">
         <v>111</v>
       </c>
-      <c r="B42" s="41">
+      <c r="B42" s="88">
         <v>6.6725975927464697E-3</v>
       </c>
-    </row>
-    <row r="43" spans="1:2">
+      <c r="C42" s="40"/>
+      <c r="D42" s="40"/>
+      <c r="E42" s="40"/>
+      <c r="F42" s="40"/>
+      <c r="G42" s="40"/>
+      <c r="H42" s="40"/>
+      <c r="I42" s="40"/>
+    </row>
+    <row r="43" spans="1:9">
       <c r="A43" t="s">
         <v>112</v>
       </c>
-      <c r="B43" s="41">
+      <c r="B43" s="88">
         <v>3.5395217114644602E-3</v>
       </c>
-    </row>
-    <row r="44" spans="1:2">
+      <c r="C43" s="40"/>
+      <c r="D43" s="40"/>
+      <c r="E43" s="40"/>
+      <c r="F43" s="40"/>
+      <c r="G43" s="40"/>
+      <c r="H43" s="40"/>
+      <c r="I43" s="40"/>
+    </row>
+    <row r="44" spans="1:9">
       <c r="A44" t="s">
-        <v>96</v>
-      </c>
-      <c r="B44" s="41">
-        <v>8.3038021272114002E-3</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2">
+        <v>153</v>
+      </c>
+      <c r="B44" s="88">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="C44" s="40"/>
+      <c r="D44" s="40"/>
+      <c r="E44" s="40"/>
+      <c r="F44" s="40"/>
+      <c r="G44" s="40"/>
+      <c r="H44" s="40"/>
+      <c r="I44" s="40"/>
+    </row>
+    <row r="45" spans="1:9">
       <c r="A45" t="s">
         <v>113</v>
       </c>
-      <c r="B45" s="41">
+      <c r="B45" s="88">
         <v>5.8650377463103599E-3</v>
       </c>
-    </row>
-    <row r="46" spans="1:2">
+      <c r="C45" s="89">
+        <v>4.3467553885149592E-2</v>
+      </c>
+      <c r="D45" s="40"/>
+      <c r="E45" s="40"/>
+      <c r="F45" s="40"/>
+      <c r="G45" s="40"/>
+      <c r="H45" s="40"/>
+      <c r="I45" s="40"/>
+    </row>
+    <row r="46" spans="1:9">
       <c r="A46" t="s">
+        <v>152</v>
+      </c>
+      <c r="B46" s="88">
+        <f>C45-SUM(B41:B45)</f>
+        <v>3.3038021272114027E-3</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9">
+      <c r="A47" t="s">
         <v>98</v>
       </c>
-      <c r="B46">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2">
-      <c r="A47" t="s">
+      <c r="B47" s="43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9">
+      <c r="A48" t="s">
         <v>99</v>
       </c>
-      <c r="B47">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2">
-      <c r="A48" t="s">
+      <c r="B48" s="43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" t="s">
         <v>100</v>
       </c>
-      <c r="B48">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2">
-      <c r="A49" t="s">
+      <c r="B49" s="43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" t="s">
         <v>101</v>
       </c>
-      <c r="B49">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2">
-      <c r="A50" t="s">
+      <c r="B50" s="43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" t="s">
         <v>102</v>
       </c>
-      <c r="B50">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2">
-      <c r="A51" t="s">
+      <c r="B51" s="43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" t="s">
         <v>103</v>
       </c>
-      <c r="B51">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2">
-      <c r="A52" t="s">
+      <c r="B52" s="43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" t="s">
         <v>104</v>
       </c>
-      <c r="B52">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2">
-      <c r="A53" t="s">
+      <c r="B53" s="43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" t="s">
         <v>105</v>
       </c>
-      <c r="B53">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2">
-      <c r="A54" t="s">
+      <c r="B54" s="43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" t="s">
         <v>106</v>
       </c>
-      <c r="B54">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2">
-      <c r="A55" t="s">
+      <c r="B55" s="43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" t="s">
         <v>107</v>
       </c>
-      <c r="B55">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2">
-      <c r="A56" t="s">
+      <c r="B56" s="43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" t="s">
         <v>108</v>
       </c>
-      <c r="B56">
-        <v>0</v>
+      <c r="B57" s="43">
+        <v>0</v>
+      </c>
+      <c r="E57" s="43" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="C58" s="87">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" t="s">
+        <v>153</v>
+      </c>
+      <c r="B59" s="88">
+        <f>B44*C58</f>
+        <v>3.15E-3</v>
+      </c>
+      <c r="C59" s="87">
+        <v>0.28000000000000003</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" t="s">
+        <v>154</v>
+      </c>
+      <c r="B60" s="88">
+        <f>$B$45*C59</f>
+        <v>1.642210568966901E-3</v>
+      </c>
+      <c r="C60" s="87">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" t="s">
+        <v>155</v>
+      </c>
+      <c r="B61" s="88">
+        <f t="shared" ref="B61:B62" si="0">$B$45*C60</f>
+        <v>1.1143571717989683E-3</v>
+      </c>
+      <c r="C61" s="87">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" t="s">
+        <v>156</v>
+      </c>
+      <c r="B62" s="88">
+        <f t="shared" si="0"/>
+        <v>1.0557067943358647E-3</v>
       </c>
     </row>
   </sheetData>
@@ -21370,13 +21585,13 @@
   <dimension ref="A1:N25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="3" width="10.83203125" style="44"/>
+    <col min="2" max="3" width="10.83203125" style="43"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" s="40"/>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
+      <c r="B1" s="44"/>
+      <c r="C1" s="44"/>
       <c r="D1" s="40"/>
       <c r="E1" s="40"/>
       <c r="F1" s="40"/>
@@ -21391,10 +21606,10 @@
     </row>
     <row r="2" spans="1:14">
       <c r="A2" s="40"/>
-      <c r="B2" s="45" t="s">
+      <c r="B2" s="44" t="s">
         <v>114</v>
       </c>
-      <c r="C2" s="45" t="s">
+      <c r="C2" s="44" t="s">
         <v>32</v>
       </c>
       <c r="D2" s="40"/>
@@ -21411,10 +21626,10 @@
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="40"/>
-      <c r="B3" s="46">
-        <v>0</v>
-      </c>
-      <c r="C3" s="43">
+      <c r="B3" s="45">
+        <v>0</v>
+      </c>
+      <c r="C3" s="42">
         <v>7.61400749455894E-2</v>
       </c>
       <c r="D3" s="40"/>
@@ -21431,10 +21646,10 @@
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="40"/>
-      <c r="B4" s="46">
+      <c r="B4" s="45">
         <v>0.5</v>
       </c>
-      <c r="C4" s="43">
+      <c r="C4" s="42">
         <v>7.5265245665851105E-2</v>
       </c>
       <c r="D4" s="40"/>
@@ -21451,10 +21666,10 @@
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="40"/>
-      <c r="B5" s="46">
+      <c r="B5" s="45">
         <v>0.7</v>
       </c>
-      <c r="C5" s="43">
+      <c r="C5" s="42">
         <v>7.4936639097747296E-2</v>
       </c>
       <c r="D5" s="40"/>
@@ -21471,10 +21686,10 @@
     </row>
     <row r="6" spans="1:14">
       <c r="A6" s="40"/>
-      <c r="B6" s="46">
+      <c r="B6" s="45">
         <v>1</v>
       </c>
-      <c r="C6" s="43">
+      <c r="C6" s="42">
         <v>7.4466879106657904E-2</v>
       </c>
       <c r="D6" s="40"/>
@@ -21491,8 +21706,8 @@
     </row>
     <row r="7" spans="1:14">
       <c r="A7" s="40"/>
-      <c r="B7" s="45"/>
-      <c r="C7" s="45"/>
+      <c r="B7" s="44"/>
+      <c r="C7" s="44"/>
       <c r="D7" s="40"/>
       <c r="E7" s="40"/>
       <c r="F7" s="40"/>
@@ -21507,8 +21722,8 @@
     </row>
     <row r="8" spans="1:14">
       <c r="A8" s="40"/>
-      <c r="B8" s="45"/>
-      <c r="C8" s="45"/>
+      <c r="B8" s="44"/>
+      <c r="C8" s="44"/>
       <c r="D8" s="40"/>
       <c r="E8" s="40"/>
       <c r="F8" s="40"/>
@@ -21523,8 +21738,8 @@
     </row>
     <row r="9" spans="1:14">
       <c r="A9" s="40"/>
-      <c r="B9" s="45"/>
-      <c r="C9" s="45"/>
+      <c r="B9" s="44"/>
+      <c r="C9" s="44"/>
       <c r="D9" s="40"/>
       <c r="E9" s="40"/>
       <c r="F9" s="40"/>
@@ -21539,8 +21754,8 @@
     </row>
     <row r="10" spans="1:14">
       <c r="A10" s="40"/>
-      <c r="B10" s="45"/>
-      <c r="C10" s="45"/>
+      <c r="B10" s="44"/>
+      <c r="C10" s="44"/>
       <c r="D10" s="40"/>
       <c r="E10" s="40"/>
       <c r="F10" s="40"/>
@@ -21555,8 +21770,8 @@
     </row>
     <row r="11" spans="1:14">
       <c r="A11" s="40"/>
-      <c r="B11" s="45"/>
-      <c r="C11" s="45"/>
+      <c r="B11" s="44"/>
+      <c r="C11" s="44"/>
       <c r="D11" s="40"/>
       <c r="E11" s="40"/>
       <c r="F11" s="40"/>
@@ -21571,8 +21786,8 @@
     </row>
     <row r="12" spans="1:14">
       <c r="A12" s="40"/>
-      <c r="B12" s="45"/>
-      <c r="C12" s="45"/>
+      <c r="B12" s="44"/>
+      <c r="C12" s="44"/>
       <c r="D12" s="40"/>
       <c r="E12" s="40"/>
       <c r="F12" s="40"/>
@@ -21587,8 +21802,8 @@
     </row>
     <row r="13" spans="1:14">
       <c r="A13" s="40"/>
-      <c r="B13" s="45"/>
-      <c r="C13" s="45"/>
+      <c r="B13" s="44"/>
+      <c r="C13" s="44"/>
       <c r="D13" s="40"/>
       <c r="E13" s="40"/>
       <c r="F13" s="40"/>
@@ -21603,8 +21818,8 @@
     </row>
     <row r="14" spans="1:14">
       <c r="A14" s="40"/>
-      <c r="B14" s="45"/>
-      <c r="C14" s="45"/>
+      <c r="B14" s="44"/>
+      <c r="C14" s="44"/>
       <c r="D14" s="40"/>
       <c r="E14" s="40"/>
       <c r="F14" s="40"/>
@@ -21619,8 +21834,8 @@
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="40"/>
-      <c r="B15" s="45"/>
-      <c r="C15" s="45"/>
+      <c r="B15" s="44"/>
+      <c r="C15" s="44"/>
       <c r="D15" s="40"/>
       <c r="E15" s="40"/>
       <c r="F15" s="40"/>
@@ -21635,8 +21850,8 @@
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="40"/>
-      <c r="B16" s="45"/>
-      <c r="C16" s="45"/>
+      <c r="B16" s="44"/>
+      <c r="C16" s="44"/>
       <c r="D16" s="40"/>
       <c r="E16" s="40"/>
       <c r="F16" s="40"/>
@@ -21651,8 +21866,8 @@
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="40"/>
-      <c r="B17" s="45"/>
-      <c r="C17" s="45"/>
+      <c r="B17" s="44"/>
+      <c r="C17" s="44"/>
       <c r="D17" s="40"/>
       <c r="E17" s="40"/>
       <c r="F17" s="40"/>
@@ -21667,8 +21882,8 @@
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="40"/>
-      <c r="B18" s="45"/>
-      <c r="C18" s="45"/>
+      <c r="B18" s="44"/>
+      <c r="C18" s="44"/>
       <c r="D18" s="40"/>
       <c r="E18" s="40"/>
       <c r="F18" s="40"/>
@@ -21683,8 +21898,8 @@
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="40"/>
-      <c r="B19" s="45"/>
-      <c r="C19" s="45"/>
+      <c r="B19" s="44"/>
+      <c r="C19" s="44"/>
       <c r="D19" s="40"/>
       <c r="E19" s="40"/>
       <c r="F19" s="40"/>
@@ -21699,8 +21914,8 @@
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="40"/>
-      <c r="B20" s="45"/>
-      <c r="C20" s="45"/>
+      <c r="B20" s="44"/>
+      <c r="C20" s="44"/>
       <c r="D20" s="40"/>
       <c r="E20" s="40"/>
       <c r="F20" s="40"/>
@@ -21715,8 +21930,8 @@
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="40"/>
-      <c r="B21" s="45"/>
-      <c r="C21" s="45"/>
+      <c r="B21" s="44"/>
+      <c r="C21" s="44"/>
       <c r="D21" s="40"/>
       <c r="E21" s="40"/>
       <c r="F21" s="40"/>
@@ -21731,8 +21946,8 @@
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="40"/>
-      <c r="B22" s="45"/>
-      <c r="C22" s="45"/>
+      <c r="B22" s="44"/>
+      <c r="C22" s="44"/>
       <c r="D22" s="40"/>
       <c r="E22" s="40"/>
       <c r="F22" s="40"/>
@@ -21747,8 +21962,8 @@
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="40"/>
-      <c r="B23" s="45"/>
-      <c r="C23" s="45"/>
+      <c r="B23" s="44"/>
+      <c r="C23" s="44"/>
       <c r="D23" s="40"/>
       <c r="E23" s="40"/>
       <c r="F23" s="40"/>
@@ -21763,8 +21978,8 @@
     </row>
     <row r="24" spans="1:14">
       <c r="A24" s="40"/>
-      <c r="B24" s="45"/>
-      <c r="C24" s="45"/>
+      <c r="B24" s="44"/>
+      <c r="C24" s="44"/>
       <c r="D24" s="40"/>
       <c r="E24" s="40"/>
       <c r="F24" s="40"/>
@@ -21779,8 +21994,8 @@
     </row>
     <row r="25" spans="1:14">
       <c r="A25" s="40"/>
-      <c r="B25" s="45"/>
-      <c r="C25" s="45"/>
+      <c r="B25" s="44"/>
+      <c r="C25" s="44"/>
       <c r="D25" s="40"/>
       <c r="E25" s="40"/>
       <c r="F25" s="40"/>
@@ -21832,7 +22047,7 @@
       <c r="B2" s="40" t="s">
         <v>115</v>
       </c>
-      <c r="C2" s="43">
+      <c r="C2" s="42">
         <f>SUM(C3:C8)</f>
         <v>3.9323104932666136E-2</v>
       </c>
@@ -21855,7 +22070,7 @@
       <c r="B3" s="40" t="s">
         <v>121</v>
       </c>
-      <c r="C3" s="43">
+      <c r="C3" s="42">
         <v>7.0898094817600603E-4</v>
       </c>
       <c r="D3" s="40"/>
@@ -21877,7 +22092,7 @@
       <c r="B4" s="40" t="s">
         <v>120</v>
       </c>
-      <c r="C4" s="43">
+      <c r="C4" s="42">
         <v>-7.31425731588811E-5</v>
       </c>
       <c r="D4" s="40"/>
@@ -21899,7 +22114,7 @@
       <c r="B5" s="40" t="s">
         <v>119</v>
       </c>
-      <c r="C5" s="43">
+      <c r="C5" s="42">
         <v>5.2595580514326603E-3</v>
       </c>
       <c r="D5" s="40"/>
@@ -21921,7 +22136,7 @@
       <c r="B6" s="40" t="s">
         <v>118</v>
       </c>
-      <c r="C6" s="43">
+      <c r="C6" s="42">
         <v>3.2283957050202399E-3</v>
       </c>
       <c r="D6" s="40"/>
@@ -21943,7 +22158,7 @@
       <c r="B7" s="40" t="s">
         <v>117</v>
       </c>
-      <c r="C7" s="43">
+      <c r="C7" s="42">
         <v>5.9454343476038098E-3</v>
       </c>
       <c r="D7" s="40"/>
@@ -21965,7 +22180,7 @@
       <c r="B8" s="40" t="s">
         <v>116</v>
       </c>
-      <c r="C8" s="43">
+      <c r="C8" s="42">
         <v>2.4253878453592299E-2</v>
       </c>
       <c r="D8" s="40"/>
@@ -22346,7 +22561,7 @@
       <c r="B32" s="40" t="s">
         <v>125</v>
       </c>
-      <c r="C32" s="47">
+      <c r="C32" s="46">
         <v>4.7471589022936803E-3</v>
       </c>
       <c r="D32" s="40"/>
@@ -22368,7 +22583,7 @@
       <c r="B33" s="40" t="s">
         <v>124</v>
       </c>
-      <c r="C33" s="47">
+      <c r="C33" s="46">
         <v>-1.8207881955470001E-3</v>
       </c>
       <c r="D33" s="40"/>
@@ -22390,7 +22605,7 @@
       <c r="B34" s="40" t="s">
         <v>123</v>
       </c>
-      <c r="C34" s="47">
+      <c r="C34" s="46">
         <v>2.33677370351318E-2</v>
       </c>
       <c r="D34" s="40"/>
@@ -22412,7 +22627,7 @@
       <c r="B35" s="40" t="s">
         <v>122</v>
       </c>
-      <c r="C35" s="47">
+      <c r="C35" s="46">
         <v>8.3822687238124197E-3</v>
       </c>
       <c r="D35" s="40"/>
@@ -22434,7 +22649,7 @@
       <c r="B36" s="40" t="s">
         <v>121</v>
       </c>
-      <c r="C36" s="47">
+      <c r="C36" s="46">
         <v>3.4695735122553702E-3</v>
       </c>
       <c r="D36" s="40"/>
@@ -22456,7 +22671,7 @@
       <c r="B37" s="40" t="s">
         <v>120</v>
       </c>
-      <c r="C37" s="47">
+      <c r="C37" s="46">
         <v>7.3740406688289203E-3</v>
       </c>
       <c r="D37" s="40"/>
@@ -22478,7 +22693,7 @@
       <c r="B38" s="40" t="s">
         <v>119</v>
       </c>
-      <c r="C38" s="47">
+      <c r="C38" s="46">
         <v>3.71489102775132E-2</v>
       </c>
       <c r="D38" s="40"/>
@@ -22500,7 +22715,7 @@
       <c r="B39" s="40" t="s">
         <v>118</v>
       </c>
-      <c r="C39" s="47">
+      <c r="C39" s="46">
         <v>8.8779764457821205E-3</v>
       </c>
       <c r="D39" s="40"/>
@@ -22522,7 +22737,7 @@
       <c r="B40" s="40" t="s">
         <v>117</v>
       </c>
-      <c r="C40" s="47">
+      <c r="C40" s="46">
         <v>1.43061710110607E-2</v>
       </c>
       <c r="D40" s="40"/>
@@ -22544,7 +22759,7 @@
       <c r="B41" s="40" t="s">
         <v>116</v>
       </c>
-      <c r="C41" s="47">
+      <c r="C41" s="46">
         <v>0.85138064675577596</v>
       </c>
       <c r="D41" s="40"/>
@@ -22683,489 +22898,489 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="41" customHeight="1">
-      <c r="A1" s="73"/>
-      <c r="B1" s="74" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="75"/>
-      <c r="D1" s="76" t="s">
+      <c r="A1" s="66"/>
+      <c r="B1" s="97" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="98"/>
+      <c r="D1" s="99" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="77"/>
+      <c r="E1" s="100"/>
     </row>
     <row r="2" spans="1:5" ht="16" customHeight="1">
-      <c r="A2" s="78" t="s">
+      <c r="A2" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="50">
+      <c r="B2" s="90">
         <v>0.5</v>
       </c>
-      <c r="C2" s="79"/>
-      <c r="D2" s="50">
+      <c r="C2" s="91"/>
+      <c r="D2" s="90">
         <v>0.36</v>
       </c>
-      <c r="E2" s="80"/>
+      <c r="E2" s="92"/>
     </row>
     <row r="3" spans="1:5" ht="16" customHeight="1">
-      <c r="A3" s="78" t="s">
+      <c r="A3" s="67" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="50" t="s">
+      <c r="B3" s="90" t="s">
         <v>140</v>
       </c>
-      <c r="C3" s="79"/>
-      <c r="D3" s="50">
+      <c r="C3" s="91"/>
+      <c r="D3" s="90">
         <v>4.4999999999999998E-2</v>
       </c>
-      <c r="E3" s="80"/>
+      <c r="E3" s="92"/>
     </row>
     <row r="4" spans="1:5" ht="16" customHeight="1">
-      <c r="A4" s="78" t="s">
+      <c r="A4" s="67" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="50">
+      <c r="B4" s="90">
         <v>0.5</v>
       </c>
-      <c r="C4" s="79"/>
-      <c r="D4" s="50">
+      <c r="C4" s="91"/>
+      <c r="D4" s="90">
         <v>0.35499999999999998</v>
       </c>
-      <c r="E4" s="80"/>
+      <c r="E4" s="92"/>
     </row>
     <row r="5" spans="1:5" ht="16" customHeight="1">
-      <c r="A5" s="78" t="s">
+      <c r="A5" s="67" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="50" t="s">
+      <c r="B5" s="90" t="s">
         <v>140</v>
       </c>
-      <c r="C5" s="79"/>
-      <c r="D5" s="50">
+      <c r="C5" s="91"/>
+      <c r="D5" s="90">
         <v>4.5000000000000012E-2</v>
       </c>
-      <c r="E5" s="80"/>
+      <c r="E5" s="92"/>
     </row>
     <row r="6" spans="1:5" ht="16" customHeight="1">
-      <c r="A6" s="78" t="s">
+      <c r="A6" s="67" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="50" t="s">
+      <c r="B6" s="90" t="s">
         <v>140</v>
       </c>
-      <c r="C6" s="79"/>
-      <c r="D6" s="50">
+      <c r="C6" s="91"/>
+      <c r="D6" s="90">
         <v>0.12</v>
       </c>
-      <c r="E6" s="80"/>
+      <c r="E6" s="92"/>
     </row>
     <row r="7" spans="1:5" ht="16" customHeight="1">
-      <c r="A7" s="78" t="s">
+      <c r="A7" s="67" t="s">
         <v>26</v>
       </c>
-      <c r="B7" s="50" t="s">
+      <c r="B7" s="90" t="s">
         <v>140</v>
       </c>
-      <c r="C7" s="79"/>
-      <c r="D7" s="50">
+      <c r="C7" s="91"/>
+      <c r="D7" s="90">
         <v>7.5000000000000011E-2</v>
       </c>
-      <c r="E7" s="80"/>
+      <c r="E7" s="92"/>
     </row>
     <row r="8" spans="1:5" ht="16" customHeight="1">
-      <c r="A8" s="81" t="s">
+      <c r="A8" s="68" t="s">
         <v>151</v>
       </c>
-      <c r="B8" s="82">
+      <c r="B8" s="93">
         <v>5.3832602562404443E-2</v>
       </c>
-      <c r="C8" s="51"/>
-      <c r="D8" s="82">
+      <c r="C8" s="94"/>
+      <c r="D8" s="93">
         <v>6.4431104932666197E-2</v>
       </c>
-      <c r="E8" s="83"/>
+      <c r="E8" s="95"/>
     </row>
     <row r="9" spans="1:5" ht="16" customHeight="1">
-      <c r="A9" s="78" t="s">
+      <c r="A9" s="67" t="s">
         <v>31</v>
       </c>
-      <c r="B9" s="52">
+      <c r="B9" s="96">
         <v>0.39013325979698232</v>
       </c>
-      <c r="C9" s="79"/>
-      <c r="D9" s="52">
+      <c r="C9" s="91"/>
+      <c r="D9" s="96">
         <v>0.52364381017028427</v>
       </c>
-      <c r="E9" s="80"/>
+      <c r="E9" s="92"/>
     </row>
     <row r="10" spans="1:5" ht="16" customHeight="1">
-      <c r="A10" s="78" t="s">
+      <c r="A10" s="67" t="s">
         <v>32</v>
       </c>
-      <c r="B10" s="50">
+      <c r="B10" s="90">
         <v>7.3904497600149111E-2</v>
       </c>
-      <c r="C10" s="79"/>
-      <c r="D10" s="50">
+      <c r="C10" s="91"/>
+      <c r="D10" s="90">
         <v>7.5095139422881152E-2</v>
       </c>
-      <c r="E10" s="80"/>
+      <c r="E10" s="92"/>
     </row>
     <row r="11" spans="1:5" ht="16" customHeight="1">
-      <c r="A11" s="99" t="s">
+      <c r="A11" s="84" t="s">
         <v>33</v>
       </c>
-      <c r="B11" s="100"/>
-      <c r="C11" s="100"/>
-      <c r="D11" s="100"/>
-      <c r="E11" s="101"/>
+      <c r="B11" s="85"/>
+      <c r="C11" s="85"/>
+      <c r="D11" s="85"/>
+      <c r="E11" s="86"/>
     </row>
     <row r="12" spans="1:5" ht="16" customHeight="1">
-      <c r="A12" s="95" t="s">
+      <c r="A12" s="80" t="s">
         <v>34</v>
       </c>
-      <c r="B12" s="96" t="s">
+      <c r="B12" s="81" t="s">
         <v>35</v>
       </c>
-      <c r="C12" s="97" t="s">
+      <c r="C12" s="82" t="s">
         <v>36</v>
       </c>
-      <c r="D12" s="96" t="s">
+      <c r="D12" s="81" t="s">
         <v>35</v>
       </c>
-      <c r="E12" s="98" t="s">
+      <c r="E12" s="83" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="16" customHeight="1">
-      <c r="A13" s="87" t="s">
+      <c r="A13" s="72" t="s">
         <v>142</v>
       </c>
       <c r="B13" s="38">
         <v>-0.1776017866289766</v>
       </c>
-      <c r="C13" s="93">
+      <c r="C13" s="78">
         <v>-0.30112278708572859</v>
       </c>
       <c r="D13" s="38">
         <v>-0.18055610612543321</v>
       </c>
-      <c r="E13" s="88">
+      <c r="E13" s="73">
         <v>-0.30363337932945272</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="16" customHeight="1">
-      <c r="A14" s="87" t="s">
+      <c r="A14" s="72" t="s">
         <v>143</v>
       </c>
       <c r="B14" s="38">
         <v>9.1966297004391961E-2</v>
       </c>
-      <c r="C14" s="93">
+      <c r="C14" s="78">
         <v>-7.981103117669619E-2</v>
       </c>
       <c r="D14" s="38">
         <v>7.8775543714589391E-2</v>
       </c>
-      <c r="E14" s="88">
+      <c r="E14" s="73">
         <v>-9.0926745737708092E-2</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="16" customHeight="1">
-      <c r="A15" s="87" t="s">
+      <c r="A15" s="72" t="s">
         <v>144</v>
       </c>
       <c r="B15" s="38">
         <v>3.3833922099381297E-2</v>
       </c>
-      <c r="C15" s="93">
+      <c r="C15" s="78">
         <v>-9.2351671693732484E-2</v>
       </c>
       <c r="D15" s="38">
         <v>6.4064379367686941E-2</v>
       </c>
-      <c r="E15" s="88">
+      <c r="E15" s="73">
         <v>-6.5811021965589744E-2</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="16" customHeight="1">
-      <c r="A16" s="87" t="s">
+      <c r="A16" s="72" t="s">
         <v>145</v>
       </c>
       <c r="B16" s="38">
         <v>-9.3805687596971943E-2</v>
       </c>
-      <c r="C16" s="93">
+      <c r="C16" s="78">
         <v>-9.6177114287752663E-2</v>
       </c>
       <c r="D16" s="38">
         <v>-9.7941054733545196E-2</v>
       </c>
-      <c r="E16" s="88">
+      <c r="E16" s="73">
         <v>-0.1003016595510592</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="16" customHeight="1">
-      <c r="A17" s="87" t="s">
+      <c r="A17" s="72" t="s">
         <v>146</v>
       </c>
       <c r="B17" s="38">
         <v>-3.1535848841887197E-2</v>
       </c>
-      <c r="C17" s="93">
+      <c r="C17" s="78">
         <v>-5.4164174740227389E-2</v>
       </c>
       <c r="D17" s="38">
         <v>-2.765350588028781E-2</v>
       </c>
-      <c r="E17" s="88">
+      <c r="E17" s="73">
         <v>-5.0372543367362743E-2</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="16" customHeight="1">
-      <c r="A18" s="87" t="s">
+      <c r="A18" s="72" t="s">
         <v>150</v>
       </c>
       <c r="B18" s="38">
         <v>-6.7084778089725683E-2</v>
       </c>
-      <c r="C18" s="93">
+      <c r="C18" s="78">
         <v>-6.8230253751904613E-2</v>
       </c>
       <c r="D18" s="38">
         <v>-7.9916796300670057E-2</v>
       </c>
-      <c r="E18" s="88">
+      <c r="E18" s="73">
         <v>-8.1046516228338472E-2</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="16" customHeight="1">
-      <c r="A19" s="87" t="s">
+      <c r="A19" s="72" t="s">
         <v>147</v>
       </c>
       <c r="B19" s="38">
         <v>-0.18876721497667329</v>
       </c>
-      <c r="C19" s="93">
+      <c r="C19" s="78">
         <v>-0.23274034313104919</v>
       </c>
       <c r="D19" s="38">
         <v>-0.1409407932870371</v>
       </c>
-      <c r="E19" s="88">
+      <c r="E19" s="73">
         <v>-0.18750636766517259</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="16" customHeight="1">
-      <c r="A20" s="87" t="s">
+      <c r="A20" s="72" t="s">
         <v>148</v>
       </c>
       <c r="B20" s="38">
         <v>-0.25987242236582753</v>
       </c>
-      <c r="C20" s="93">
+      <c r="C20" s="78">
         <v>-0.27210455637801051</v>
       </c>
       <c r="D20" s="38">
         <v>-0.29538143519201682</v>
       </c>
-      <c r="E20" s="88">
+      <c r="E20" s="73">
         <v>-0.30702670956451628</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="16" customHeight="1">
-      <c r="A21" s="87" t="s">
+      <c r="A21" s="72" t="s">
         <v>149</v>
       </c>
       <c r="B21" s="38">
         <v>-8.9207423756033855E-2</v>
       </c>
-      <c r="C21" s="93">
+      <c r="C21" s="78">
         <v>-8.5983283903999119E-2</v>
       </c>
       <c r="D21" s="38">
         <v>-0.1092578089622447</v>
       </c>
-      <c r="E21" s="88">
+      <c r="E21" s="73">
         <v>-0.10610464602381051</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="16" customHeight="1">
-      <c r="A22" s="84" t="s">
+      <c r="A22" s="69" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="85"/>
-      <c r="C22" s="92"/>
-      <c r="D22" s="85"/>
-      <c r="E22" s="86"/>
+      <c r="B22" s="70"/>
+      <c r="C22" s="77"/>
+      <c r="D22" s="70"/>
+      <c r="E22" s="71"/>
     </row>
     <row r="23" spans="1:5" ht="16" customHeight="1">
-      <c r="A23" s="87" t="s">
+      <c r="A23" s="72" t="s">
         <v>38</v>
       </c>
       <c r="B23" s="38">
         <v>5.4343730281515963E-2</v>
       </c>
-      <c r="C23" s="93">
+      <c r="C23" s="78">
         <v>5.6344567324771777E-2</v>
       </c>
       <c r="D23" s="38">
         <v>5.7861316067238773E-2</v>
       </c>
-      <c r="E23" s="88">
+      <c r="E23" s="73">
         <v>5.9854710537364908E-2</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="16" customHeight="1">
-      <c r="A24" s="87" t="s">
+      <c r="A24" s="72" t="s">
         <v>39</v>
       </c>
       <c r="B24" s="38">
         <v>0.1623335163683407</v>
       </c>
-      <c r="C24" s="93">
+      <c r="C24" s="78">
         <v>0.1812045715294813</v>
       </c>
       <c r="D24" s="38">
         <v>0.19742360658304531</v>
       </c>
-      <c r="E24" s="88">
+      <c r="E24" s="73">
         <v>0.21512829632760089</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="16" customHeight="1">
-      <c r="A25" s="87" t="s">
+      <c r="A25" s="72" t="s">
         <v>40</v>
       </c>
       <c r="B25" s="38">
         <v>0.1909841808946714</v>
       </c>
-      <c r="C25" s="93">
+      <c r="C25" s="78">
         <v>0.24478438742884201</v>
       </c>
       <c r="D25" s="38">
         <v>0.1823803443255978</v>
       </c>
-      <c r="E25" s="88">
+      <c r="E25" s="73">
         <v>0.2323129793194352</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="16" hidden="1" customHeight="1">
-      <c r="A26" s="84" t="s">
+      <c r="A26" s="69" t="s">
         <v>41</v>
       </c>
-      <c r="B26" s="85"/>
-      <c r="C26" s="92"/>
-      <c r="D26" s="85"/>
-      <c r="E26" s="86"/>
+      <c r="B26" s="70"/>
+      <c r="C26" s="77"/>
+      <c r="D26" s="70"/>
+      <c r="E26" s="71"/>
     </row>
     <row r="27" spans="1:5" ht="16" hidden="1" customHeight="1">
-      <c r="A27" s="87" t="s">
+      <c r="A27" s="72" t="s">
         <v>38</v>
       </c>
       <c r="B27" s="38">
         <v>7.1864010159486513E-2</v>
       </c>
-      <c r="C27" s="93">
+      <c r="C27" s="78">
         <v>7.3827777470207856E-2</v>
       </c>
       <c r="D27" s="38">
         <v>8.023634617565778E-2</v>
       </c>
-      <c r="E27" s="88">
+      <c r="E27" s="73">
         <v>8.2182399142831541E-2</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="16" hidden="1" customHeight="1">
-      <c r="A28" s="87" t="s">
+      <c r="A28" s="72" t="s">
         <v>39</v>
       </c>
       <c r="B28" s="38">
         <v>0.1974163616175966</v>
       </c>
-      <c r="C28" s="93">
+      <c r="C28" s="78">
         <v>0.21563136088152421</v>
       </c>
       <c r="D28" s="38">
         <v>0.22128131377722929</v>
       </c>
-      <c r="E28" s="88">
+      <c r="E28" s="73">
         <v>0.24041734846749269</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="16" hidden="1" customHeight="1">
-      <c r="A29" s="87" t="s">
+      <c r="A29" s="72" t="s">
         <v>40</v>
       </c>
       <c r="B29" s="38">
         <v>0.24037887766160429</v>
       </c>
-      <c r="C29" s="93">
+      <c r="C29" s="78">
         <v>0.28832371414060048</v>
       </c>
       <c r="D29" s="38">
         <v>0.23717115075981349</v>
       </c>
-      <c r="E29" s="88">
+      <c r="E29" s="73">
         <v>0.28471072762898181</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="16" customHeight="1">
-      <c r="A30" s="84" t="s">
+      <c r="A30" s="69" t="s">
         <v>42</v>
       </c>
-      <c r="B30" s="85"/>
-      <c r="C30" s="92"/>
-      <c r="D30" s="85"/>
-      <c r="E30" s="86"/>
+      <c r="B30" s="70"/>
+      <c r="C30" s="77"/>
+      <c r="D30" s="70"/>
+      <c r="E30" s="71"/>
     </row>
     <row r="31" spans="1:5" ht="16" customHeight="1">
-      <c r="A31" s="87" t="s">
+      <c r="A31" s="72" t="s">
         <v>38</v>
       </c>
       <c r="B31" s="38">
         <v>0.3473</v>
       </c>
-      <c r="C31" s="93">
+      <c r="C31" s="78">
         <v>0.38829999999999998</v>
       </c>
       <c r="D31" s="38">
         <v>0.30495</v>
       </c>
-      <c r="E31" s="88">
+      <c r="E31" s="73">
         <v>0.34620000000000001</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="16" customHeight="1">
-      <c r="A32" s="87" t="s">
+      <c r="A32" s="72" t="s">
         <v>39</v>
       </c>
       <c r="B32" s="38">
         <v>0.19</v>
       </c>
-      <c r="C32" s="93">
+      <c r="C32" s="78">
         <v>0.26274999999999998</v>
       </c>
       <c r="D32" s="38">
         <v>0.16594999999999999</v>
       </c>
-      <c r="E32" s="88">
+      <c r="E32" s="73">
         <v>0.23294999999999999</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="16" customHeight="1">
-      <c r="A33" s="89" t="s">
+      <c r="A33" s="74" t="s">
         <v>40</v>
       </c>
-      <c r="B33" s="90">
+      <c r="B33" s="75">
         <v>0.1142</v>
       </c>
-      <c r="C33" s="94">
+      <c r="C33" s="79">
         <v>0.19855</v>
       </c>
-      <c r="D33" s="90">
+      <c r="D33" s="75">
         <v>9.1550000000000006E-2</v>
       </c>
-      <c r="E33" s="91">
+      <c r="E33" s="76">
         <v>0.15820000000000001</v>
       </c>
     </row>
@@ -23243,6 +23458,18 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="D6:E6"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="D10:E10"/>
     <mergeCell ref="B7:C7"/>
@@ -23251,24 +23478,12 @@
     <mergeCell ref="D8:E8"/>
     <mergeCell ref="B9:C9"/>
     <mergeCell ref="D9:E9"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="D3:E3"/>
   </mergeCells>
   <conditionalFormatting sqref="B13:E21">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -23292,27 +23507,27 @@
   <sheetData>
     <row r="1" spans="1:10" ht="24" customHeight="1">
       <c r="A1" s="1"/>
-      <c r="B1" s="53" t="s">
+      <c r="B1" s="101" t="s">
         <v>44</v>
       </c>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
-      <c r="F1" s="54"/>
-      <c r="G1" s="54"/>
+      <c r="C1" s="102"/>
+      <c r="D1" s="102"/>
+      <c r="E1" s="102"/>
+      <c r="F1" s="102"/>
+      <c r="G1" s="102"/>
       <c r="H1" s="3"/>
-      <c r="I1" s="53" t="s">
+      <c r="I1" s="101" t="s">
         <v>45</v>
       </c>
-      <c r="J1" s="54"/>
+      <c r="J1" s="102"/>
     </row>
     <row r="2" spans="1:10" ht="49" customHeight="1">
       <c r="A2" s="4"/>
-      <c r="B2" s="55" t="s">
+      <c r="B2" s="103" t="s">
         <v>46</v>
       </c>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
+      <c r="C2" s="102"/>
+      <c r="D2" s="102"/>
       <c r="E2" s="2" t="s">
         <v>32</v>
       </c>
@@ -26786,7 +27001,7 @@
       <c r="B2">
         <v>1.43303265158561E-2</v>
       </c>
-      <c r="C2" s="48">
+      <c r="C2" s="47">
         <v>0.110773577218248</v>
       </c>
     </row>
@@ -26797,7 +27012,7 @@
       <c r="B3">
         <v>1.9304864315867198E-2</v>
       </c>
-      <c r="C3" s="48">
+      <c r="C3" s="47">
         <v>0.110182258707823</v>
       </c>
     </row>
@@ -26808,7 +27023,7 @@
       <c r="B4">
         <v>2.2797451977775302E-2</v>
       </c>
-      <c r="C4" s="48">
+      <c r="C4" s="47">
         <v>9.2534243769205105E-2</v>
       </c>
     </row>
@@ -26819,7 +27034,7 @@
       <c r="B5">
         <v>2.6134514674963399E-2</v>
       </c>
-      <c r="C5" s="48">
+      <c r="C5" s="47">
         <v>7.7144923837934101E-2</v>
       </c>
     </row>
@@ -26830,7 +27045,7 @@
       <c r="B6">
         <v>3.2554216155495599E-2</v>
       </c>
-      <c r="C6" s="48">
+      <c r="C6" s="47">
         <v>2.69296484689278E-2</v>
       </c>
     </row>

--- a/epsilon-phi-core/src/Scripts/Case Studies/1. Portfolio Analysis/Simple Portfolio Report_new_pe.xlsx
+++ b/epsilon-phi-core/src/Scripts/Case Studies/1. Portfolio Analysis/Simple Portfolio Report_new_pe.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/francisbarker/repo/epsilon-psi/epsilon-phi-core/src/Scripts/Case Studies/1. Portfolio Analysis/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/francisbarker/Repositories/Python/epsilon-phi/epsilon-phi-core/src/Scripts/Case Studies/1. Portfolio Analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CB2D1C3-6880-DC48-8FC8-04065BF04204}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{061DF6AC-6E24-2742-8C00-96F375277F48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="19040" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1196,6 +1196,16 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="10" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1208,16 +1218,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
     <xf numFmtId="2" fontId="10" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -22051,7 +22051,9 @@
         <f>SUM(C3:C8)</f>
         <v>3.9323104932666136E-2</v>
       </c>
-      <c r="D2" s="40"/>
+      <c r="D2" s="42">
+        <v>2.23946383044141E-2</v>
+      </c>
       <c r="E2" s="40"/>
       <c r="F2" s="40"/>
       <c r="G2" s="40"/>
@@ -22073,7 +22075,9 @@
       <c r="C3" s="42">
         <v>7.0898094817600603E-4</v>
       </c>
-      <c r="D3" s="40"/>
+      <c r="D3" s="42">
+        <v>5.1102386495189001E-3</v>
+      </c>
       <c r="E3" s="40"/>
       <c r="F3" s="40"/>
       <c r="G3" s="40"/>
@@ -22095,7 +22099,9 @@
       <c r="C4" s="42">
         <v>-7.31425731588811E-5</v>
       </c>
-      <c r="D4" s="40"/>
+      <c r="D4" s="42">
+        <v>1.4935013698618501E-4</v>
+      </c>
       <c r="E4" s="40"/>
       <c r="F4" s="40"/>
       <c r="G4" s="40"/>
@@ -22117,7 +22123,9 @@
       <c r="C5" s="42">
         <v>5.2595580514326603E-3</v>
       </c>
-      <c r="D5" s="40"/>
+      <c r="D5" s="42">
+        <v>2.4458062675070699E-4</v>
+      </c>
       <c r="E5" s="40"/>
       <c r="F5" s="40"/>
       <c r="G5" s="40"/>
@@ -22139,7 +22147,9 @@
       <c r="C6" s="42">
         <v>3.2283957050202399E-3</v>
       </c>
-      <c r="D6" s="40"/>
+      <c r="D6" s="42">
+        <v>2.52168605647219E-4</v>
+      </c>
       <c r="E6" s="40"/>
       <c r="F6" s="40"/>
       <c r="G6" s="40"/>
@@ -22161,7 +22171,9 @@
       <c r="C7" s="42">
         <v>5.9454343476038098E-3</v>
       </c>
-      <c r="D7" s="40"/>
+      <c r="D7" s="42">
+        <v>6.8162623908724399E-4</v>
+      </c>
       <c r="E7" s="40"/>
       <c r="F7" s="40"/>
       <c r="G7" s="40"/>
@@ -22246,7 +22258,9 @@
     <row r="12" spans="1:14">
       <c r="A12" s="40"/>
       <c r="B12" s="40"/>
-      <c r="C12" s="40"/>
+      <c r="C12" s="40">
+        <v>0</v>
+      </c>
       <c r="D12" s="40"/>
       <c r="E12" s="40"/>
       <c r="F12" s="40"/>
@@ -22261,8 +22275,12 @@
     </row>
     <row r="13" spans="1:14">
       <c r="A13" s="40"/>
-      <c r="B13" s="40"/>
-      <c r="C13" s="40"/>
+      <c r="B13" s="40">
+        <v>0</v>
+      </c>
+      <c r="C13" s="40">
+        <v>2.23946383044141E-2</v>
+      </c>
       <c r="D13" s="40"/>
       <c r="E13" s="40"/>
       <c r="F13" s="40"/>
@@ -22277,8 +22295,12 @@
     </row>
     <row r="14" spans="1:14">
       <c r="A14" s="40"/>
-      <c r="B14" s="40"/>
-      <c r="C14" s="40"/>
+      <c r="B14" s="40">
+        <v>1</v>
+      </c>
+      <c r="C14" s="40">
+        <v>5.1102386495189001E-3</v>
+      </c>
       <c r="D14" s="40"/>
       <c r="E14" s="40"/>
       <c r="F14" s="40"/>
@@ -22293,8 +22315,12 @@
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="40"/>
-      <c r="B15" s="40"/>
-      <c r="C15" s="40"/>
+      <c r="B15" s="40">
+        <v>2</v>
+      </c>
+      <c r="C15" s="40">
+        <v>1.4935013698618501E-4</v>
+      </c>
       <c r="D15" s="40"/>
       <c r="E15" s="40"/>
       <c r="F15" s="40"/>
@@ -22309,8 +22335,12 @@
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="40"/>
-      <c r="B16" s="40"/>
-      <c r="C16" s="40"/>
+      <c r="B16" s="40">
+        <v>3</v>
+      </c>
+      <c r="C16" s="40">
+        <v>2.4458062675070699E-4</v>
+      </c>
       <c r="D16" s="40"/>
       <c r="E16" s="40"/>
       <c r="F16" s="40"/>
@@ -22325,8 +22355,12 @@
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="40"/>
-      <c r="B17" s="40"/>
-      <c r="C17" s="40"/>
+      <c r="B17" s="40">
+        <v>4</v>
+      </c>
+      <c r="C17" s="40">
+        <v>2.52168605647219E-4</v>
+      </c>
       <c r="D17" s="40"/>
       <c r="E17" s="40"/>
       <c r="F17" s="40"/>
@@ -22341,8 +22375,12 @@
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="40"/>
-      <c r="B18" s="40"/>
-      <c r="C18" s="40"/>
+      <c r="B18" s="40">
+        <v>5</v>
+      </c>
+      <c r="C18" s="40">
+        <v>6.8162623908724399E-4</v>
+      </c>
       <c r="D18" s="40"/>
       <c r="E18" s="40"/>
       <c r="F18" s="40"/>
@@ -22899,131 +22937,131 @@
   <sheetData>
     <row r="1" spans="1:5" ht="41" customHeight="1">
       <c r="A1" s="66"/>
-      <c r="B1" s="97" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="98"/>
-      <c r="D1" s="99" t="s">
+      <c r="B1" s="90" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="91"/>
+      <c r="D1" s="92" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="100"/>
+      <c r="E1" s="93"/>
     </row>
     <row r="2" spans="1:5" ht="16" customHeight="1">
       <c r="A2" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="90">
+      <c r="B2" s="94">
         <v>0.5</v>
       </c>
-      <c r="C2" s="91"/>
-      <c r="D2" s="90">
+      <c r="C2" s="95"/>
+      <c r="D2" s="94">
         <v>0.36</v>
       </c>
-      <c r="E2" s="92"/>
+      <c r="E2" s="96"/>
     </row>
     <row r="3" spans="1:5" ht="16" customHeight="1">
       <c r="A3" s="67" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="90" t="s">
+      <c r="B3" s="94" t="s">
         <v>140</v>
       </c>
-      <c r="C3" s="91"/>
-      <c r="D3" s="90">
+      <c r="C3" s="95"/>
+      <c r="D3" s="94">
         <v>4.4999999999999998E-2</v>
       </c>
-      <c r="E3" s="92"/>
+      <c r="E3" s="96"/>
     </row>
     <row r="4" spans="1:5" ht="16" customHeight="1">
       <c r="A4" s="67" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="90">
+      <c r="B4" s="94">
         <v>0.5</v>
       </c>
-      <c r="C4" s="91"/>
-      <c r="D4" s="90">
+      <c r="C4" s="95"/>
+      <c r="D4" s="94">
         <v>0.35499999999999998</v>
       </c>
-      <c r="E4" s="92"/>
+      <c r="E4" s="96"/>
     </row>
     <row r="5" spans="1:5" ht="16" customHeight="1">
       <c r="A5" s="67" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="90" t="s">
+      <c r="B5" s="94" t="s">
         <v>140</v>
       </c>
-      <c r="C5" s="91"/>
-      <c r="D5" s="90">
+      <c r="C5" s="95"/>
+      <c r="D5" s="94">
         <v>4.5000000000000012E-2</v>
       </c>
-      <c r="E5" s="92"/>
+      <c r="E5" s="96"/>
     </row>
     <row r="6" spans="1:5" ht="16" customHeight="1">
       <c r="A6" s="67" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="90" t="s">
+      <c r="B6" s="94" t="s">
         <v>140</v>
       </c>
-      <c r="C6" s="91"/>
-      <c r="D6" s="90">
+      <c r="C6" s="95"/>
+      <c r="D6" s="94">
         <v>0.12</v>
       </c>
-      <c r="E6" s="92"/>
+      <c r="E6" s="96"/>
     </row>
     <row r="7" spans="1:5" ht="16" customHeight="1">
       <c r="A7" s="67" t="s">
         <v>26</v>
       </c>
-      <c r="B7" s="90" t="s">
+      <c r="B7" s="94" t="s">
         <v>140</v>
       </c>
-      <c r="C7" s="91"/>
-      <c r="D7" s="90">
+      <c r="C7" s="95"/>
+      <c r="D7" s="94">
         <v>7.5000000000000011E-2</v>
       </c>
-      <c r="E7" s="92"/>
+      <c r="E7" s="96"/>
     </row>
     <row r="8" spans="1:5" ht="16" customHeight="1">
       <c r="A8" s="68" t="s">
         <v>151</v>
       </c>
-      <c r="B8" s="93">
+      <c r="B8" s="97">
         <v>5.3832602562404443E-2</v>
       </c>
-      <c r="C8" s="94"/>
-      <c r="D8" s="93">
+      <c r="C8" s="98"/>
+      <c r="D8" s="97">
         <v>6.4431104932666197E-2</v>
       </c>
-      <c r="E8" s="95"/>
+      <c r="E8" s="99"/>
     </row>
     <row r="9" spans="1:5" ht="16" customHeight="1">
       <c r="A9" s="67" t="s">
         <v>31</v>
       </c>
-      <c r="B9" s="96">
+      <c r="B9" s="100">
         <v>0.39013325979698232</v>
       </c>
-      <c r="C9" s="91"/>
-      <c r="D9" s="96">
+      <c r="C9" s="95"/>
+      <c r="D9" s="100">
         <v>0.52364381017028427</v>
       </c>
-      <c r="E9" s="92"/>
+      <c r="E9" s="96"/>
     </row>
     <row r="10" spans="1:5" ht="16" customHeight="1">
       <c r="A10" s="67" t="s">
         <v>32</v>
       </c>
-      <c r="B10" s="90">
+      <c r="B10" s="94">
         <v>7.3904497600149111E-2</v>
       </c>
-      <c r="C10" s="91"/>
-      <c r="D10" s="90">
+      <c r="C10" s="95"/>
+      <c r="D10" s="94">
         <v>7.5095139422881152E-2</v>
       </c>
-      <c r="E10" s="92"/>
+      <c r="E10" s="96"/>
     </row>
     <row r="11" spans="1:5" ht="16" customHeight="1">
       <c r="A11" s="84" t="s">
@@ -23458,18 +23496,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="D6:E6"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="D10:E10"/>
     <mergeCell ref="B7:C7"/>
@@ -23478,6 +23504,18 @@
     <mergeCell ref="D8:E8"/>
     <mergeCell ref="B9:C9"/>
     <mergeCell ref="D9:E9"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="D3:E3"/>
   </mergeCells>
   <conditionalFormatting sqref="B13:E21">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
